--- a/research/traditional_assets/database/data/australia/australia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_beverage_alcoholic.xlsx
@@ -1665,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1802,22 +1802,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07572430455246293</v>
+        <v>0.07552863163880552</v>
       </c>
       <c r="C2">
-        <v>6276.597991077208</v>
+        <v>6244.602911097742</v>
       </c>
       <c r="D2">
-        <v>5970.997991077207</v>
+        <v>6010.298911097741</v>
       </c>
       <c r="E2">
-        <v>-1440.2</v>
+        <v>-1368.904</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>71.29599999999999</v>
       </c>
       <c r="G2">
         <v>305.6</v>
@@ -1838,28 +1838,28 @@
         <v>274.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.5861888</v>
       </c>
       <c r="N2">
-        <v>274.4</v>
+        <v>270.8138112</v>
       </c>
       <c r="O2">
-        <v>82.31999999999999</v>
+        <v>81.24414336</v>
       </c>
       <c r="P2">
-        <v>192.08</v>
+        <v>189.56966784</v>
       </c>
       <c r="Q2">
-        <v>246.88</v>
+        <v>244.36966784</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07572430455246293</v>
+        <v>0.07593589054424801</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6959789964029562</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>76.51577072573535</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1884,22 +1884,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07552863163880552</v>
+        <v>0.07533295872514814</v>
       </c>
       <c r="C3">
-        <v>6244.602911097742</v>
+        <v>6213.128613719255</v>
       </c>
       <c r="D3">
-        <v>6010.298911097741</v>
+        <v>6050.120613719254</v>
       </c>
       <c r="E3">
-        <v>-1368.904</v>
+        <v>-1297.608</v>
       </c>
       <c r="F3">
-        <v>71.29599999999999</v>
+        <v>142.592</v>
       </c>
       <c r="G3">
         <v>305.6</v>
@@ -1920,28 +1920,28 @@
         <v>274.4</v>
       </c>
       <c r="M3">
-        <v>3.5861888</v>
+        <v>7.172377599999999</v>
       </c>
       <c r="N3">
-        <v>270.8138112</v>
+        <v>267.2276224</v>
       </c>
       <c r="O3">
-        <v>81.24414336</v>
+        <v>80.16828671999998</v>
       </c>
       <c r="P3">
-        <v>189.56966784</v>
+        <v>187.05933568</v>
       </c>
       <c r="Q3">
-        <v>244.36966784</v>
+        <v>241.85933568</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07593589054424801</v>
+        <v>0.0761517946174981</v>
       </c>
       <c r="T3">
-        <v>0.6959789964029562</v>
+        <v>0.7009652336604641</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>76.51577072573535</v>
+        <v>38.25788536286768</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1966,22 +1966,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07533295872514814</v>
+        <v>0.07513728581149075</v>
       </c>
       <c r="C4">
-        <v>6213.128613719255</v>
+        <v>6182.185519440391</v>
       </c>
       <c r="D4">
-        <v>6050.120613719254</v>
+        <v>6090.47351944039</v>
       </c>
       <c r="E4">
-        <v>-1297.608</v>
+        <v>-1226.312</v>
       </c>
       <c r="F4">
-        <v>142.592</v>
+        <v>213.888</v>
       </c>
       <c r="G4">
         <v>305.6</v>
@@ -2002,28 +2002,28 @@
         <v>274.4</v>
       </c>
       <c r="M4">
-        <v>7.172377599999999</v>
+        <v>10.7585664</v>
       </c>
       <c r="N4">
-        <v>267.2276224</v>
+        <v>263.6414336</v>
       </c>
       <c r="O4">
-        <v>80.16828671999998</v>
+        <v>79.09243007999999</v>
       </c>
       <c r="P4">
-        <v>187.05933568</v>
+        <v>184.54900352</v>
       </c>
       <c r="Q4">
-        <v>241.85933568</v>
+        <v>239.34900352</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0761517946174981</v>
+        <v>0.07637215032112449</v>
       </c>
       <c r="T4">
-        <v>0.7009652336604641</v>
+        <v>0.7060542799335908</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.25788536286768</v>
+        <v>25.50525690857845</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2048,22 +2048,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07513728581149075</v>
+        <v>0.07494161289783337</v>
       </c>
       <c r="C5">
-        <v>6182.185519440391</v>
+        <v>6151.784328635754</v>
       </c>
       <c r="D5">
-        <v>6090.47351944039</v>
+        <v>6131.368328635754</v>
       </c>
       <c r="E5">
-        <v>-1226.312</v>
+        <v>-1155.016</v>
       </c>
       <c r="F5">
-        <v>213.888</v>
+        <v>285.184</v>
       </c>
       <c r="G5">
         <v>305.6</v>
@@ -2084,28 +2084,28 @@
         <v>274.4</v>
       </c>
       <c r="M5">
-        <v>10.7585664</v>
+        <v>14.3447552</v>
       </c>
       <c r="N5">
-        <v>263.6414336</v>
+        <v>260.0552448</v>
       </c>
       <c r="O5">
-        <v>79.09243007999999</v>
+        <v>78.01657343999999</v>
       </c>
       <c r="P5">
-        <v>184.54900352</v>
+        <v>182.03867136</v>
       </c>
       <c r="Q5">
-        <v>239.34900352</v>
+        <v>236.83867136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07637215032112449</v>
+        <v>0.07659709676857643</v>
       </c>
       <c r="T5">
-        <v>0.7060542799335908</v>
+        <v>0.7112493480040742</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.50525690857845</v>
+        <v>19.12894268143384</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2130,22 +2130,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07494161289783337</v>
+        <v>0.07474593998417596</v>
       </c>
       <c r="C6">
-        <v>6151.784328635754</v>
+        <v>6121.936031015664</v>
       </c>
       <c r="D6">
-        <v>6131.368328635754</v>
+        <v>6172.816031015665</v>
       </c>
       <c r="E6">
-        <v>-1155.016</v>
+        <v>-1083.72</v>
       </c>
       <c r="F6">
-        <v>285.184</v>
+        <v>356.48</v>
       </c>
       <c r="G6">
         <v>305.6</v>
@@ -2166,28 +2166,28 @@
         <v>274.4</v>
       </c>
       <c r="M6">
-        <v>14.3447552</v>
+        <v>17.930944</v>
       </c>
       <c r="N6">
-        <v>260.0552448</v>
+        <v>256.469056</v>
       </c>
       <c r="O6">
-        <v>78.01657343999999</v>
+        <v>76.94071679999999</v>
       </c>
       <c r="P6">
-        <v>182.03867136</v>
+        <v>179.5283392</v>
       </c>
       <c r="Q6">
-        <v>236.83867136</v>
+        <v>234.3283392</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07659709676857643</v>
+        <v>0.07682677893071155</v>
       </c>
       <c r="T6">
-        <v>0.7112493480040742</v>
+        <v>0.7165537859286731</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.12894268143384</v>
+        <v>15.30315414514707</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2212,22 +2212,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07474593998417596</v>
+        <v>0.07455026707051859</v>
       </c>
       <c r="C7">
-        <v>6121.936031015664</v>
+        <v>6092.651915472151</v>
       </c>
       <c r="D7">
-        <v>6172.816031015665</v>
+        <v>6214.82791547215</v>
       </c>
       <c r="E7">
-        <v>-1083.72</v>
+        <v>-1012.424</v>
       </c>
       <c r="F7">
-        <v>356.48</v>
+        <v>427.776</v>
       </c>
       <c r="G7">
         <v>305.6</v>
@@ -2248,28 +2248,28 @@
         <v>274.4</v>
       </c>
       <c r="M7">
-        <v>17.930944</v>
+        <v>21.5171328</v>
       </c>
       <c r="N7">
-        <v>256.469056</v>
+        <v>252.8828672</v>
       </c>
       <c r="O7">
-        <v>76.94071679999999</v>
+        <v>75.86486015999999</v>
       </c>
       <c r="P7">
-        <v>179.5283392</v>
+        <v>177.01800704</v>
       </c>
       <c r="Q7">
-        <v>234.3283392</v>
+        <v>231.81800704</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07682677893071155</v>
+        <v>0.07706134794736021</v>
       </c>
       <c r="T7">
-        <v>0.7165537859286731</v>
+        <v>0.7219710842346465</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.30315414514707</v>
+        <v>12.75262845428922</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2294,22 +2294,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07455026707051859</v>
+        <v>0.0743545941568612</v>
       </c>
       <c r="C8">
-        <v>6092.651915472151</v>
+        <v>6063.94358032984</v>
       </c>
       <c r="D8">
-        <v>6214.82791547215</v>
+        <v>6257.41558032984</v>
       </c>
       <c r="E8">
-        <v>-1012.424</v>
+        <v>-941.1280000000002</v>
       </c>
       <c r="F8">
-        <v>427.776</v>
+        <v>499.0719999999999</v>
       </c>
       <c r="G8">
         <v>305.6</v>
@@ -2330,28 +2330,28 @@
         <v>274.4</v>
       </c>
       <c r="M8">
-        <v>21.5171328</v>
+        <v>25.10332159999999</v>
       </c>
       <c r="N8">
-        <v>252.8828672</v>
+        <v>249.2966784</v>
       </c>
       <c r="O8">
-        <v>75.86486015999999</v>
+        <v>74.78900351999999</v>
       </c>
       <c r="P8">
-        <v>177.01800704</v>
+        <v>174.50767488</v>
       </c>
       <c r="Q8">
-        <v>231.81800704</v>
+        <v>229.30767488</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07706134794736021</v>
+        <v>0.07730096145899054</v>
       </c>
       <c r="T8">
-        <v>0.7219710842346465</v>
+        <v>0.7275048835794581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.75262845428923</v>
+        <v>10.93082438939077</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2376,22 +2376,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0743545941568612</v>
+        <v>0.07415892124320382</v>
       </c>
       <c r="C9">
-        <v>6063.94358032984</v>
+        <v>6035.82294402114</v>
       </c>
       <c r="D9">
-        <v>6257.41558032984</v>
+        <v>6300.590944021139</v>
       </c>
       <c r="E9">
-        <v>-941.128</v>
+        <v>-869.8320000000001</v>
       </c>
       <c r="F9">
-        <v>499.072</v>
+        <v>570.3679999999999</v>
       </c>
       <c r="G9">
         <v>305.6</v>
@@ -2412,28 +2412,28 @@
         <v>274.4</v>
       </c>
       <c r="M9">
-        <v>25.1033216</v>
+        <v>28.6895104</v>
       </c>
       <c r="N9">
-        <v>249.2966784</v>
+        <v>245.7104896</v>
       </c>
       <c r="O9">
-        <v>74.78900351999999</v>
+        <v>73.71314688</v>
       </c>
       <c r="P9">
-        <v>174.50767488</v>
+        <v>171.99734272</v>
       </c>
       <c r="Q9">
-        <v>229.30767488</v>
+        <v>226.79734272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07730096145899054</v>
+        <v>0.07754578396000415</v>
       </c>
       <c r="T9">
-        <v>0.7275048835794581</v>
+        <v>0.7331589829100263</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.93082438939077</v>
+        <v>9.564471340716921</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2458,22 +2458,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07415892124320382</v>
+        <v>0.07405774832954642</v>
       </c>
       <c r="C10">
-        <v>6035.82294402114</v>
+        <v>5987.08532822557</v>
       </c>
       <c r="D10">
-        <v>6300.590944021139</v>
+        <v>6323.14932822557</v>
       </c>
       <c r="E10">
-        <v>-869.8320000000001</v>
+        <v>-798.5360000000002</v>
       </c>
       <c r="F10">
-        <v>570.3679999999999</v>
+        <v>641.6639999999999</v>
       </c>
       <c r="G10">
         <v>305.6</v>
@@ -2494,45 +2494,45 @@
         <v>274.4</v>
       </c>
       <c r="M10">
-        <v>28.6895104</v>
+        <v>33.23819519999999</v>
       </c>
       <c r="N10">
-        <v>245.7104896</v>
+        <v>241.1618048</v>
       </c>
       <c r="O10">
-        <v>73.71314688</v>
+        <v>72.34854143999999</v>
       </c>
       <c r="P10">
-        <v>171.99734272</v>
+        <v>168.81326336</v>
       </c>
       <c r="Q10">
-        <v>226.79734272</v>
+        <v>223.61326336</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07754578396000415</v>
+        <v>0.07779598717532574</v>
       </c>
       <c r="T10">
-        <v>0.7331589829100263</v>
+        <v>0.7389373481599476</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.564471340716921</v>
+        <v>8.255562564359693</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2540,22 +2540,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07405774832954642</v>
+        <v>0.07387257541588903</v>
       </c>
       <c r="C11">
-        <v>5987.08532822557</v>
+        <v>5957.498219100456</v>
       </c>
       <c r="D11">
-        <v>6323.14932822557</v>
+        <v>6364.858219100456</v>
       </c>
       <c r="E11">
-        <v>-798.5360000000002</v>
+        <v>-727.2400000000001</v>
       </c>
       <c r="F11">
-        <v>641.6639999999999</v>
+        <v>712.9599999999999</v>
       </c>
       <c r="G11">
         <v>305.6</v>
@@ -2576,28 +2576,28 @@
         <v>274.4</v>
       </c>
       <c r="M11">
-        <v>33.23819519999999</v>
+        <v>36.93132799999999</v>
       </c>
       <c r="N11">
-        <v>241.1618048</v>
+        <v>237.468672</v>
       </c>
       <c r="O11">
-        <v>72.34854143999999</v>
+        <v>71.24060159999999</v>
       </c>
       <c r="P11">
-        <v>168.81326336</v>
+        <v>166.2280704</v>
       </c>
       <c r="Q11">
-        <v>223.61326336</v>
+        <v>221.0280704</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07779598717532574</v>
+        <v>0.07805175046209892</v>
       </c>
       <c r="T11">
-        <v>0.7389373481599476</v>
+        <v>0.7448441215265339</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.255562564359693</v>
+        <v>7.430006307923723</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2622,22 +2622,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07387257541588903</v>
+        <v>0.07368740250223164</v>
       </c>
       <c r="C12">
-        <v>5957.498219100456</v>
+        <v>5928.465005724368</v>
       </c>
       <c r="D12">
-        <v>6364.858219100456</v>
+        <v>6407.121005724368</v>
       </c>
       <c r="E12">
-        <v>-727.24</v>
+        <v>-655.9440000000001</v>
       </c>
       <c r="F12">
-        <v>712.96</v>
+        <v>784.256</v>
       </c>
       <c r="G12">
         <v>305.6</v>
@@ -2658,28 +2658,28 @@
         <v>274.4</v>
       </c>
       <c r="M12">
-        <v>36.931328</v>
+        <v>40.62446079999999</v>
       </c>
       <c r="N12">
-        <v>237.468672</v>
+        <v>233.7755392</v>
       </c>
       <c r="O12">
-        <v>71.24060159999999</v>
+        <v>70.13266175999999</v>
       </c>
       <c r="P12">
-        <v>166.2280704</v>
+        <v>163.64287744</v>
       </c>
       <c r="Q12">
-        <v>221.0280704</v>
+        <v>218.44287744</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07805175046209892</v>
+        <v>0.07831326123846252</v>
       </c>
       <c r="T12">
-        <v>0.7448441215265339</v>
+        <v>0.7508836313732683</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.430006307923722</v>
+        <v>6.754551189021566</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2704,22 +2704,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07368740250223164</v>
+        <v>0.07364502958857426</v>
       </c>
       <c r="C13">
-        <v>5928.465005724368</v>
+        <v>5866.918982261631</v>
       </c>
       <c r="D13">
-        <v>6407.121005724368</v>
+        <v>6416.87098226163</v>
       </c>
       <c r="E13">
-        <v>-655.9440000000001</v>
+        <v>-584.6480000000001</v>
       </c>
       <c r="F13">
-        <v>784.256</v>
+        <v>855.5519999999999</v>
       </c>
       <c r="G13">
         <v>305.6</v>
@@ -2740,45 +2740,45 @@
         <v>274.4</v>
       </c>
       <c r="M13">
-        <v>40.62446079999999</v>
+        <v>45.772032</v>
       </c>
       <c r="N13">
-        <v>233.7755392</v>
+        <v>228.627968</v>
       </c>
       <c r="O13">
-        <v>70.13266175999999</v>
+        <v>68.58839039999999</v>
       </c>
       <c r="P13">
-        <v>163.64287744</v>
+        <v>160.0395776</v>
       </c>
       <c r="Q13">
-        <v>218.44287744</v>
+        <v>214.8395776</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07831326123846252</v>
+        <v>0.07858071544156166</v>
       </c>
       <c r="T13">
-        <v>0.7508836313732683</v>
+        <v>0.7570604028074284</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.754551189021566</v>
+        <v>5.994927207950917</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2786,22 +2786,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07364502958857426</v>
+        <v>0.07354455667491686</v>
       </c>
       <c r="C14">
-        <v>5866.918982261631</v>
+        <v>5818.86075577179</v>
       </c>
       <c r="D14">
-        <v>6416.87098226163</v>
+        <v>6440.108755771789</v>
       </c>
       <c r="E14">
-        <v>-584.6480000000001</v>
+        <v>-513.3520000000001</v>
       </c>
       <c r="F14">
-        <v>855.5519999999999</v>
+        <v>926.848</v>
       </c>
       <c r="G14">
         <v>305.6</v>
@@ -2822,45 +2822,45 @@
         <v>274.4</v>
       </c>
       <c r="M14">
-        <v>45.772032</v>
+        <v>50.3278464</v>
       </c>
       <c r="N14">
-        <v>228.627968</v>
+        <v>224.0721536</v>
       </c>
       <c r="O14">
-        <v>68.58839039999999</v>
+        <v>67.22164607999999</v>
       </c>
       <c r="P14">
-        <v>160.0395776</v>
+        <v>156.85050752</v>
       </c>
       <c r="Q14">
-        <v>214.8395776</v>
+        <v>211.65050752</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07858071544156166</v>
+        <v>0.07885431801714582</v>
       </c>
       <c r="T14">
-        <v>0.7570604028074284</v>
+        <v>0.7633791689872014</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>5.994927207950917</v>
+        <v>5.452249989381624</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2868,22 +2868,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07354455667491686</v>
+        <v>0.07337688376125948</v>
       </c>
       <c r="C15">
-        <v>5818.86075577179</v>
+        <v>5786.721892187167</v>
       </c>
       <c r="D15">
-        <v>6440.108755771789</v>
+        <v>6479.265892187167</v>
       </c>
       <c r="E15">
-        <v>-513.3520000000001</v>
+        <v>-442.056</v>
       </c>
       <c r="F15">
-        <v>926.848</v>
+        <v>998.144</v>
       </c>
       <c r="G15">
         <v>305.6</v>
@@ -2904,28 +2904,28 @@
         <v>274.4</v>
       </c>
       <c r="M15">
-        <v>50.3278464</v>
+        <v>54.1992192</v>
       </c>
       <c r="N15">
-        <v>224.0721536</v>
+        <v>220.2007808</v>
       </c>
       <c r="O15">
-        <v>67.22164607999999</v>
+        <v>66.06023423999999</v>
       </c>
       <c r="P15">
-        <v>156.85050752</v>
+        <v>154.14054656</v>
       </c>
       <c r="Q15">
-        <v>211.65050752</v>
+        <v>208.94054656</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07885431801714582</v>
+        <v>0.07913428344332497</v>
       </c>
       <c r="T15">
-        <v>0.7633791689872014</v>
+        <v>0.7698448832176666</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.452249989381624</v>
+        <v>5.06280356156865</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2950,22 +2950,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07337688376125948</v>
+        <v>0.07320921084760208</v>
       </c>
       <c r="C16">
-        <v>5786.721892187167</v>
+        <v>5755.062107784343</v>
       </c>
       <c r="D16">
-        <v>6479.265892187167</v>
+        <v>6518.902107784343</v>
       </c>
       <c r="E16">
-        <v>-442.056</v>
+        <v>-370.76</v>
       </c>
       <c r="F16">
-        <v>998.144</v>
+        <v>1069.44</v>
       </c>
       <c r="G16">
         <v>305.6</v>
@@ -2986,28 +2986,28 @@
         <v>274.4</v>
       </c>
       <c r="M16">
-        <v>54.1992192</v>
+        <v>58.070592</v>
       </c>
       <c r="N16">
-        <v>220.2007808</v>
+        <v>216.329408</v>
       </c>
       <c r="O16">
-        <v>66.06023423999999</v>
+        <v>64.89882239999999</v>
       </c>
       <c r="P16">
-        <v>154.14054656</v>
+        <v>151.4305856</v>
       </c>
       <c r="Q16">
-        <v>208.94054656</v>
+        <v>206.2305856</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07913428344332497</v>
+        <v>0.07942083629129658</v>
       </c>
       <c r="T16">
-        <v>0.7698448832176666</v>
+        <v>0.7764627319006137</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.06280356156865</v>
+        <v>4.72528332413074</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3032,22 +3032,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07320921084760208</v>
+        <v>0.07304153793394469</v>
       </c>
       <c r="C17">
-        <v>5755.062107784343</v>
+        <v>5723.89024882623</v>
       </c>
       <c r="D17">
-        <v>6518.902107784343</v>
+        <v>6559.02624882623</v>
       </c>
       <c r="E17">
-        <v>-370.7600000000002</v>
+        <v>-299.4640000000002</v>
       </c>
       <c r="F17">
-        <v>1069.44</v>
+        <v>1140.736</v>
       </c>
       <c r="G17">
         <v>305.6</v>
@@ -3068,28 +3068,28 @@
         <v>274.4</v>
       </c>
       <c r="M17">
-        <v>58.07059199999999</v>
+        <v>61.94196479999999</v>
       </c>
       <c r="N17">
-        <v>216.329408</v>
+        <v>212.4580352</v>
       </c>
       <c r="O17">
-        <v>64.8988224</v>
+        <v>63.73741055999999</v>
       </c>
       <c r="P17">
-        <v>151.4305856</v>
+        <v>148.72062464</v>
       </c>
       <c r="Q17">
-        <v>206.2305856</v>
+        <v>203.52062464</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07942083629129658</v>
+        <v>0.07971421182612465</v>
       </c>
       <c r="T17">
-        <v>0.7764627319006137</v>
+        <v>0.7832381484093449</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.725283324130741</v>
+        <v>4.42995311637257</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3114,22 +3114,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07304153793394469</v>
+        <v>0.0729928650202873</v>
       </c>
       <c r="C18">
-        <v>5723.89024882623</v>
+        <v>5664.334347489886</v>
       </c>
       <c r="D18">
-        <v>6559.02624882623</v>
+        <v>6570.766347489885</v>
       </c>
       <c r="E18">
-        <v>-299.4640000000002</v>
+        <v>-228.1680000000001</v>
       </c>
       <c r="F18">
-        <v>1140.736</v>
+        <v>1212.032</v>
       </c>
       <c r="G18">
         <v>305.6</v>
@@ -3150,45 +3150,45 @@
         <v>274.4</v>
       </c>
       <c r="M18">
-        <v>61.94196479999999</v>
+        <v>67.0253696</v>
       </c>
       <c r="N18">
-        <v>212.4580352</v>
+        <v>207.3746304</v>
       </c>
       <c r="O18">
-        <v>63.73741055999999</v>
+        <v>62.21238911999999</v>
       </c>
       <c r="P18">
-        <v>148.72062464</v>
+        <v>145.16224128</v>
       </c>
       <c r="Q18">
-        <v>203.52062464</v>
+        <v>199.96224128</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07971421182612465</v>
+        <v>0.08001465665094858</v>
       </c>
       <c r="T18">
-        <v>0.7832381484093449</v>
+        <v>0.7901768279664796</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.42995311637257</v>
+        <v>4.093972202430048</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3196,22 +3196,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0729928650202873</v>
+        <v>0.07283219210662992</v>
       </c>
       <c r="C19">
-        <v>5664.334347489886</v>
+        <v>5632.093418194054</v>
       </c>
       <c r="D19">
-        <v>6570.766347489885</v>
+        <v>6609.821418194054</v>
       </c>
       <c r="E19">
-        <v>-228.1680000000001</v>
+        <v>-156.8720000000001</v>
       </c>
       <c r="F19">
-        <v>1212.032</v>
+        <v>1283.328</v>
       </c>
       <c r="G19">
         <v>305.6</v>
@@ -3232,28 +3232,28 @@
         <v>274.4</v>
       </c>
       <c r="M19">
-        <v>67.0253696</v>
+        <v>70.9680384</v>
       </c>
       <c r="N19">
-        <v>207.3746304</v>
+        <v>203.4319616</v>
       </c>
       <c r="O19">
-        <v>62.21238911999999</v>
+        <v>61.02958847999999</v>
       </c>
       <c r="P19">
-        <v>145.16224128</v>
+        <v>142.40237312</v>
       </c>
       <c r="Q19">
-        <v>199.96224128</v>
+        <v>197.20237312</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08001465665094858</v>
+        <v>0.08032242939832918</v>
       </c>
       <c r="T19">
-        <v>0.7901768279664796</v>
+        <v>0.7972847436103734</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.093972202430048</v>
+        <v>3.866529302295045</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3278,22 +3278,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07283219210662993</v>
+        <v>0.07267151919297254</v>
       </c>
       <c r="C20">
-        <v>5632.093418194052</v>
+        <v>5600.319532979954</v>
       </c>
       <c r="D20">
-        <v>6609.821418194051</v>
+        <v>6649.343532979953</v>
       </c>
       <c r="E20">
-        <v>-156.8720000000003</v>
+        <v>-85.57600000000002</v>
       </c>
       <c r="F20">
-        <v>1283.328</v>
+        <v>1354.624</v>
       </c>
       <c r="G20">
         <v>305.6</v>
@@ -3314,28 +3314,28 @@
         <v>274.4</v>
       </c>
       <c r="M20">
-        <v>70.96803839999998</v>
+        <v>74.9107072</v>
       </c>
       <c r="N20">
-        <v>203.4319616</v>
+        <v>199.4892928</v>
       </c>
       <c r="O20">
-        <v>61.02958847999999</v>
+        <v>59.84678783999999</v>
       </c>
       <c r="P20">
-        <v>142.40237312</v>
+        <v>139.64250496</v>
       </c>
       <c r="Q20">
-        <v>197.20237312</v>
+        <v>194.44250496</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08032242939832918</v>
+        <v>0.08063780147280561</v>
       </c>
       <c r="T20">
-        <v>0.7972847436103734</v>
+        <v>0.80456816334424</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.866529302295046</v>
+        <v>3.66302776006899</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3360,22 +3360,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07267151919297254</v>
+        <v>0.07251084627931516</v>
       </c>
       <c r="C21">
-        <v>5600.319532979954</v>
+        <v>5569.021120034323</v>
       </c>
       <c r="D21">
-        <v>6649.343532979953</v>
+        <v>6689.341120034323</v>
       </c>
       <c r="E21">
-        <v>-85.57600000000002</v>
+        <v>-14.27999999999997</v>
       </c>
       <c r="F21">
-        <v>1354.624</v>
+        <v>1425.92</v>
       </c>
       <c r="G21">
         <v>305.6</v>
@@ -3396,28 +3396,28 @@
         <v>274.4</v>
       </c>
       <c r="M21">
-        <v>74.9107072</v>
+        <v>78.85337600000001</v>
       </c>
       <c r="N21">
-        <v>199.4892928</v>
+        <v>195.546624</v>
       </c>
       <c r="O21">
-        <v>59.84678783999999</v>
+        <v>58.66398719999998</v>
       </c>
       <c r="P21">
-        <v>139.64250496</v>
+        <v>136.8826368</v>
       </c>
       <c r="Q21">
-        <v>194.44250496</v>
+        <v>191.6826368</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08063780147280561</v>
+        <v>0.08096105784914394</v>
       </c>
       <c r="T21">
-        <v>0.80456816334424</v>
+        <v>0.8120336685714533</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.66302776006899</v>
+        <v>3.47987637206554</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3442,22 +3442,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07251084627931516</v>
+        <v>0.07235017336565777</v>
       </c>
       <c r="C22">
-        <v>5569.021120034323</v>
+        <v>5538.206811562345</v>
       </c>
       <c r="D22">
-        <v>6689.341120034323</v>
+        <v>6729.822811562345</v>
       </c>
       <c r="E22">
-        <v>-14.27999999999997</v>
+        <v>57.01600000000008</v>
       </c>
       <c r="F22">
-        <v>1425.92</v>
+        <v>1497.216</v>
       </c>
       <c r="G22">
         <v>305.6</v>
@@ -3478,28 +3478,28 @@
         <v>274.4</v>
       </c>
       <c r="M22">
-        <v>78.85337600000001</v>
+        <v>82.7960448</v>
       </c>
       <c r="N22">
-        <v>195.546624</v>
+        <v>191.6039552</v>
       </c>
       <c r="O22">
-        <v>58.66398719999998</v>
+        <v>57.48118655999999</v>
       </c>
       <c r="P22">
-        <v>136.8826368</v>
+        <v>134.12276864</v>
       </c>
       <c r="Q22">
-        <v>191.6826368</v>
+        <v>188.92276864</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08096105784914394</v>
+        <v>0.08129249793121236</v>
       </c>
       <c r="T22">
-        <v>0.8120336685714533</v>
+        <v>0.8196881739310011</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.47987637206554</v>
+        <v>3.314167973395753</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3524,22 +3524,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07235017336565776</v>
+        <v>0.07218950045200039</v>
       </c>
       <c r="C23">
-        <v>5538.20681156235</v>
+        <v>5507.885449998509</v>
       </c>
       <c r="D23">
-        <v>6729.822811562349</v>
+        <v>6770.797449998508</v>
       </c>
       <c r="E23">
-        <v>57.01599999999985</v>
+        <v>128.3119999999999</v>
       </c>
       <c r="F23">
-        <v>1497.216</v>
+        <v>1568.512</v>
       </c>
       <c r="G23">
         <v>305.6</v>
@@ -3560,28 +3560,28 @@
         <v>274.4</v>
       </c>
       <c r="M23">
-        <v>82.79604479999999</v>
+        <v>86.7387136</v>
       </c>
       <c r="N23">
-        <v>191.6039552</v>
+        <v>187.6612864</v>
       </c>
       <c r="O23">
-        <v>57.48118655999999</v>
+        <v>56.29838591999999</v>
       </c>
       <c r="P23">
-        <v>134.12276864</v>
+        <v>131.36290048</v>
       </c>
       <c r="Q23">
-        <v>188.92276864</v>
+        <v>186.16290048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08129249793121235</v>
+        <v>0.08163243647692356</v>
       </c>
       <c r="T23">
-        <v>0.8196881739310009</v>
+        <v>0.8275389486587423</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.314167973395753</v>
+        <v>3.163523974605037</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3606,22 +3606,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07218950045200039</v>
+        <v>0.07202882753834298</v>
       </c>
       <c r="C24">
-        <v>5507.885449998509</v>
+        <v>5478.06609444573</v>
       </c>
       <c r="D24">
-        <v>6770.797449998508</v>
+        <v>6812.27409444573</v>
       </c>
       <c r="E24">
-        <v>128.3119999999999</v>
+        <v>199.6079999999999</v>
       </c>
       <c r="F24">
-        <v>1568.512</v>
+        <v>1639.808</v>
       </c>
       <c r="G24">
         <v>305.6</v>
@@ -3642,28 +3642,28 @@
         <v>274.4</v>
       </c>
       <c r="M24">
-        <v>86.7387136</v>
+        <v>90.6813824</v>
       </c>
       <c r="N24">
-        <v>187.6612864</v>
+        <v>183.7186176</v>
       </c>
       <c r="O24">
-        <v>56.29838591999999</v>
+        <v>55.11558527999998</v>
       </c>
       <c r="P24">
-        <v>131.36290048</v>
+        <v>128.60303232</v>
       </c>
       <c r="Q24">
-        <v>186.16290048</v>
+        <v>183.40303232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08163243647692356</v>
+        <v>0.08198120459525063</v>
       </c>
       <c r="T24">
-        <v>0.8275389486587423</v>
+        <v>0.8355936396131781</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.163523974605037</v>
+        <v>3.025979453970035</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3688,22 +3688,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07202882753834298</v>
+        <v>0.0722881546246856</v>
       </c>
       <c r="C25">
-        <v>5478.06609444573</v>
+        <v>5340.075860086591</v>
       </c>
       <c r="D25">
-        <v>6812.27409444573</v>
+        <v>6745.579860086591</v>
       </c>
       <c r="E25">
-        <v>199.6079999999999</v>
+        <v>270.904</v>
       </c>
       <c r="F25">
-        <v>1639.808</v>
+        <v>1711.104</v>
       </c>
       <c r="G25">
         <v>305.6</v>
@@ -3724,45 +3724,45 @@
         <v>274.4</v>
       </c>
       <c r="M25">
-        <v>90.6813824</v>
+        <v>98.90181120000001</v>
       </c>
       <c r="N25">
-        <v>183.7186176</v>
+        <v>175.4981888</v>
       </c>
       <c r="O25">
-        <v>55.11558527999998</v>
+        <v>52.64945663999999</v>
       </c>
       <c r="P25">
-        <v>128.60303232</v>
+        <v>122.84873216</v>
       </c>
       <c r="Q25">
-        <v>183.40303232</v>
+        <v>177.64873216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08198120459525063</v>
+        <v>0.08233915082195473</v>
       </c>
       <c r="T25">
-        <v>0.8355936396131781</v>
+        <v>0.8438602961190467</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.025979453970035</v>
+        <v>2.774468906793893</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3770,22 +3770,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0722881546246856</v>
+        <v>0.07214498171102822</v>
       </c>
       <c r="C26">
-        <v>5340.075860086592</v>
+        <v>5305.43899819003</v>
       </c>
       <c r="D26">
-        <v>6745.579860086591</v>
+        <v>6782.23899819003</v>
       </c>
       <c r="E26">
-        <v>270.9039999999998</v>
+        <v>342.1999999999998</v>
       </c>
       <c r="F26">
-        <v>1711.104</v>
+        <v>1782.4</v>
       </c>
       <c r="G26">
         <v>305.6</v>
@@ -3806,28 +3806,28 @@
         <v>274.4</v>
       </c>
       <c r="M26">
-        <v>98.9018112</v>
+        <v>103.02272</v>
       </c>
       <c r="N26">
-        <v>175.4981888</v>
+        <v>171.37728</v>
       </c>
       <c r="O26">
-        <v>52.64945663999999</v>
+        <v>51.41318399999999</v>
       </c>
       <c r="P26">
-        <v>122.84873216</v>
+        <v>119.964096</v>
       </c>
       <c r="Q26">
-        <v>177.64873216</v>
+        <v>174.764096</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08233915082195473</v>
+        <v>0.08270664228137095</v>
       </c>
       <c r="T26">
-        <v>0.8438602961190467</v>
+        <v>0.8523473967984049</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.774468906793893</v>
+        <v>2.663490150522137</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3852,22 +3852,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07214498171102822</v>
+        <v>0.07200180879737082</v>
       </c>
       <c r="C27">
-        <v>5305.43899819003</v>
+        <v>5271.20276478863</v>
       </c>
       <c r="D27">
-        <v>6782.23899819003</v>
+        <v>6819.298764788629</v>
       </c>
       <c r="E27">
-        <v>342.1999999999998</v>
+        <v>413.4959999999999</v>
       </c>
       <c r="F27">
-        <v>1782.4</v>
+        <v>1853.696</v>
       </c>
       <c r="G27">
         <v>305.6</v>
@@ -3888,28 +3888,28 @@
         <v>274.4</v>
       </c>
       <c r="M27">
-        <v>103.02272</v>
+        <v>107.1436288</v>
       </c>
       <c r="N27">
-        <v>171.37728</v>
+        <v>167.2563712</v>
       </c>
       <c r="O27">
-        <v>51.41318399999999</v>
+        <v>50.17691136</v>
       </c>
       <c r="P27">
-        <v>119.964096</v>
+        <v>117.07945984</v>
       </c>
       <c r="Q27">
-        <v>174.764096</v>
+        <v>171.87945984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08270664228137095</v>
+        <v>0.083084065942393</v>
       </c>
       <c r="T27">
-        <v>0.8523473967984049</v>
+        <v>0.8610638785772051</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.663490150522137</v>
+        <v>2.561048221655901</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3934,22 +3934,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07200180879737082</v>
+        <v>0.07252013588371342</v>
       </c>
       <c r="C28">
-        <v>5271.20276478863</v>
+        <v>5067.623483182751</v>
       </c>
       <c r="D28">
-        <v>6819.298764788629</v>
+        <v>6687.015483182751</v>
       </c>
       <c r="E28">
-        <v>413.4959999999999</v>
+        <v>484.7919999999999</v>
       </c>
       <c r="F28">
-        <v>1853.696</v>
+        <v>1924.992</v>
       </c>
       <c r="G28">
         <v>305.6</v>
@@ -3970,45 +3970,45 @@
         <v>274.4</v>
       </c>
       <c r="M28">
-        <v>107.1436288</v>
+        <v>118.0020096</v>
       </c>
       <c r="N28">
-        <v>167.2563712</v>
+        <v>156.3979904</v>
       </c>
       <c r="O28">
-        <v>50.17691136</v>
+        <v>46.91939711999999</v>
       </c>
       <c r="P28">
-        <v>117.07945984</v>
+        <v>109.47859328</v>
       </c>
       <c r="Q28">
-        <v>171.87945984</v>
+        <v>164.27859328</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.083084065942393</v>
+        <v>0.08347182997768962</v>
       </c>
       <c r="T28">
-        <v>0.8610638785772051</v>
+        <v>0.8700191680759727</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.561048221655901</v>
+        <v>2.325384126339489</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4016,22 +4016,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07252013588371342</v>
+        <v>0.07295026297005602</v>
       </c>
       <c r="C29">
-        <v>5067.623483182751</v>
+        <v>4890.388675544627</v>
       </c>
       <c r="D29">
-        <v>6687.015483182751</v>
+        <v>6581.076675544627</v>
       </c>
       <c r="E29">
-        <v>484.7919999999999</v>
+        <v>556.088</v>
       </c>
       <c r="F29">
-        <v>1924.992</v>
+        <v>1996.288</v>
       </c>
       <c r="G29">
         <v>305.6</v>
@@ -4052,45 +4052,45 @@
         <v>274.4</v>
       </c>
       <c r="M29">
-        <v>118.0020096</v>
+        <v>127.9620608</v>
       </c>
       <c r="N29">
-        <v>156.3979904</v>
+        <v>146.4379392</v>
       </c>
       <c r="O29">
-        <v>46.91939711999999</v>
+        <v>43.93138175999999</v>
       </c>
       <c r="P29">
-        <v>109.47859328</v>
+        <v>102.50655744</v>
       </c>
       <c r="Q29">
-        <v>164.27859328</v>
+        <v>157.30655744</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08347182997768962</v>
+        <v>0.08387036523618893</v>
       </c>
       <c r="T29">
-        <v>0.8700191680759727</v>
+        <v>0.8792232156163725</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.325384126339489</v>
+        <v>2.144385595890622</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4098,22 +4098,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07295026297005602</v>
+        <v>0.07285119005639866</v>
       </c>
       <c r="C30">
-        <v>4890.388675544627</v>
+        <v>4843.195365292817</v>
       </c>
       <c r="D30">
-        <v>6581.076675544627</v>
+        <v>6605.179365292817</v>
       </c>
       <c r="E30">
-        <v>556.088</v>
+        <v>627.3840000000002</v>
       </c>
       <c r="F30">
-        <v>1996.288</v>
+        <v>2067.584</v>
       </c>
       <c r="G30">
         <v>305.6</v>
@@ -4134,28 +4134,28 @@
         <v>274.4</v>
       </c>
       <c r="M30">
-        <v>127.9620608</v>
+        <v>132.5321344</v>
       </c>
       <c r="N30">
-        <v>146.4379392</v>
+        <v>141.8678656</v>
       </c>
       <c r="O30">
-        <v>43.93138175999999</v>
+        <v>42.56035967999998</v>
       </c>
       <c r="P30">
-        <v>102.50655744</v>
+        <v>99.30750591999998</v>
       </c>
       <c r="Q30">
-        <v>157.30655744</v>
+        <v>154.10750592</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08387036523618893</v>
+        <v>0.08428012683999811</v>
       </c>
       <c r="T30">
-        <v>0.8792232156163725</v>
+        <v>0.8886865321015726</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.144385595890622</v>
+        <v>2.070441264997841</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4180,22 +4180,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07285119005639866</v>
+        <v>0.07275211714274125</v>
       </c>
       <c r="C31">
-        <v>4843.195365292818</v>
+        <v>4796.179252527041</v>
       </c>
       <c r="D31">
-        <v>6605.179365292817</v>
+        <v>6629.459252527041</v>
       </c>
       <c r="E31">
-        <v>627.3839999999998</v>
+        <v>698.6799999999996</v>
       </c>
       <c r="F31">
-        <v>2067.584</v>
+        <v>2138.88</v>
       </c>
       <c r="G31">
         <v>305.6</v>
@@ -4216,28 +4216,28 @@
         <v>274.4</v>
       </c>
       <c r="M31">
-        <v>132.5321344</v>
+        <v>137.102208</v>
       </c>
       <c r="N31">
-        <v>141.8678656</v>
+        <v>137.297792</v>
       </c>
       <c r="O31">
-        <v>42.56035968</v>
+        <v>41.18933759999999</v>
       </c>
       <c r="P31">
-        <v>99.30750591999998</v>
+        <v>96.1084544</v>
       </c>
       <c r="Q31">
-        <v>154.10750592</v>
+        <v>150.9084544</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08428012683999811</v>
+        <v>0.08470159591820181</v>
       </c>
       <c r="T31">
-        <v>0.8886865321015726</v>
+        <v>0.8984202290577781</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.070441264997842</v>
+        <v>2.001426556164581</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4262,22 +4262,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07275211714274125</v>
+        <v>0.07519194422908387</v>
       </c>
       <c r="C32">
-        <v>4796.179252527041</v>
+        <v>4174.571434906111</v>
       </c>
       <c r="D32">
-        <v>6629.459252527041</v>
+        <v>6079.147434906111</v>
       </c>
       <c r="E32">
-        <v>698.6799999999996</v>
+        <v>769.9759999999999</v>
       </c>
       <c r="F32">
-        <v>2138.88</v>
+        <v>2210.176</v>
       </c>
       <c r="G32">
         <v>305.6</v>
@@ -4298,45 +4298,45 @@
         <v>274.4</v>
       </c>
       <c r="M32">
-        <v>137.102208</v>
+        <v>167.5313408</v>
       </c>
       <c r="N32">
-        <v>137.297792</v>
+        <v>106.8686592</v>
       </c>
       <c r="O32">
-        <v>41.18933759999999</v>
+        <v>32.06059775999999</v>
       </c>
       <c r="P32">
-        <v>96.1084544</v>
+        <v>74.80806143999999</v>
       </c>
       <c r="Q32">
-        <v>150.9084544</v>
+        <v>129.60806144</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08470159591820181</v>
+        <v>0.08513528149142591</v>
       </c>
       <c r="T32">
-        <v>0.8984202290577781</v>
+        <v>0.9084360621576417</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.04487</v>
+        <v>0.05306</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.001426556164581</v>
+        <v>1.63790248851157</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4344,22 +4344,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07519194422908387</v>
+        <v>0.07517477131542648</v>
       </c>
       <c r="C33">
-        <v>4174.571434906111</v>
+        <v>4106.829391901698</v>
       </c>
       <c r="D33">
-        <v>6079.147434906111</v>
+        <v>6082.701391901697</v>
       </c>
       <c r="E33">
-        <v>769.9759999999999</v>
+        <v>841.2719999999997</v>
       </c>
       <c r="F33">
-        <v>2210.176</v>
+        <v>2281.472</v>
       </c>
       <c r="G33">
         <v>305.6</v>
@@ -4380,28 +4380,28 @@
         <v>274.4</v>
       </c>
       <c r="M33">
-        <v>167.5313408</v>
+        <v>172.9355776</v>
       </c>
       <c r="N33">
-        <v>106.8686592</v>
+        <v>101.4644224</v>
       </c>
       <c r="O33">
-        <v>32.06059775999999</v>
+        <v>30.43932672</v>
       </c>
       <c r="P33">
-        <v>74.80806143999999</v>
+        <v>71.02509567999999</v>
       </c>
       <c r="Q33">
-        <v>129.60806144</v>
+        <v>125.82509568</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08513528149142591</v>
+        <v>0.085581722522686</v>
       </c>
       <c r="T33">
-        <v>0.9084360621576417</v>
+        <v>0.9187464785839721</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.63790248851157</v>
+        <v>1.586718035745584</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4426,22 +4426,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07517477131542648</v>
+        <v>0.0751575984017691</v>
       </c>
       <c r="C34">
-        <v>4106.829391901698</v>
+        <v>4039.091506716718</v>
       </c>
       <c r="D34">
-        <v>6082.701391901697</v>
+        <v>6086.259506716718</v>
       </c>
       <c r="E34">
-        <v>841.2719999999997</v>
+        <v>912.568</v>
       </c>
       <c r="F34">
-        <v>2281.472</v>
+        <v>2352.768</v>
       </c>
       <c r="G34">
         <v>305.6</v>
@@ -4462,28 +4462,28 @@
         <v>274.4</v>
       </c>
       <c r="M34">
-        <v>172.9355776</v>
+        <v>178.3398144</v>
       </c>
       <c r="N34">
-        <v>101.4644224</v>
+        <v>96.06018559999995</v>
       </c>
       <c r="O34">
-        <v>30.43932672</v>
+        <v>28.81805567999999</v>
       </c>
       <c r="P34">
-        <v>71.02509567999999</v>
+        <v>67.24212991999997</v>
       </c>
       <c r="Q34">
-        <v>125.82509568</v>
+        <v>122.04212992</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.085581722522686</v>
+        <v>0.08604149015189418</v>
       </c>
       <c r="T34">
-        <v>0.9187464785839721</v>
+        <v>0.9293646686349691</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.586718035745584</v>
+        <v>1.53863567102602</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4508,22 +4508,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0751575984017691</v>
+        <v>0.07852002548811171</v>
       </c>
       <c r="C35">
-        <v>4039.091506716718</v>
+        <v>3342.34966691045</v>
       </c>
       <c r="D35">
-        <v>6086.259506716718</v>
+        <v>5460.81366691045</v>
       </c>
       <c r="E35">
-        <v>912.568</v>
+        <v>983.8639999999998</v>
       </c>
       <c r="F35">
-        <v>2352.768</v>
+        <v>2424.064</v>
       </c>
       <c r="G35">
         <v>305.6</v>
@@ -4544,45 +4544,45 @@
         <v>274.4</v>
       </c>
       <c r="M35">
-        <v>178.3398144</v>
+        <v>218.16576</v>
       </c>
       <c r="N35">
-        <v>96.06018559999995</v>
+        <v>56.23424</v>
       </c>
       <c r="O35">
-        <v>28.81805567999999</v>
+        <v>16.870272</v>
       </c>
       <c r="P35">
-        <v>67.24212991999997</v>
+        <v>39.363968</v>
       </c>
       <c r="Q35">
-        <v>122.04212992</v>
+        <v>94.16396800000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08604149015189418</v>
+        <v>0.08651519013350259</v>
       </c>
       <c r="T35">
-        <v>0.9293646686349691</v>
+        <v>0.9403046220208446</v>
       </c>
       <c r="U35">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.53863567102602</v>
+        <v>1.257759237746565</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4590,22 +4590,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07852002548811171</v>
+        <v>0.0867448125489112</v>
       </c>
       <c r="C36">
-        <v>3342.34966691045</v>
+        <v>2174.113009644296</v>
       </c>
       <c r="D36">
-        <v>5460.81366691045</v>
+        <v>4363.873009644296</v>
       </c>
       <c r="E36">
-        <v>983.8639999999998</v>
+        <v>1055.16</v>
       </c>
       <c r="F36">
-        <v>2424.064</v>
+        <v>2495.36</v>
       </c>
       <c r="G36">
         <v>305.6</v>
@@ -4626,45 +4626,45 @@
         <v>274.4</v>
       </c>
       <c r="M36">
-        <v>218.16576</v>
+        <v>295.949696</v>
       </c>
       <c r="N36">
-        <v>56.23424</v>
+        <v>-21.54969600000004</v>
       </c>
       <c r="O36">
-        <v>16.870272</v>
+        <v>-6.464908800000011</v>
       </c>
       <c r="P36">
-        <v>39.363968</v>
+        <v>-15.08478720000003</v>
       </c>
       <c r="Q36">
-        <v>94.16396800000001</v>
+        <v>39.71521279999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08651519013350259</v>
+        <v>0.08735544977142257</v>
       </c>
       <c r="T36">
-        <v>0.9403046220208446</v>
+        <v>0.9597101563838929</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.3</v>
+        <v>0.278155379487195</v>
       </c>
       <c r="W36">
-        <v>0.063</v>
+        <v>0.08561077199281869</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.257759237746565</v>
+        <v>0.9271845982906499</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4672,22 +4672,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0867448125489112</v>
+        <v>0.08747281254891121</v>
       </c>
       <c r="C37">
-        <v>2174.113009644296</v>
+        <v>2026.582665075104</v>
       </c>
       <c r="D37">
-        <v>4363.873009644296</v>
+        <v>4287.638665075104</v>
       </c>
       <c r="E37">
-        <v>1055.16</v>
+        <v>1126.456</v>
       </c>
       <c r="F37">
-        <v>2495.36</v>
+        <v>2566.656</v>
       </c>
       <c r="G37">
         <v>305.6</v>
@@ -4708,37 +4708,37 @@
         <v>274.4</v>
       </c>
       <c r="M37">
-        <v>295.949696</v>
+        <v>304.4054016</v>
       </c>
       <c r="N37">
-        <v>-21.54969600000004</v>
+        <v>-30.00540160000003</v>
       </c>
       <c r="O37">
-        <v>-6.464908800000011</v>
+        <v>-9.001620480000009</v>
       </c>
       <c r="P37">
-        <v>-15.08478720000003</v>
+        <v>-21.00378112000002</v>
       </c>
       <c r="Q37">
-        <v>39.71521279999998</v>
+        <v>33.79621887999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08735544977142257</v>
+        <v>0.08800475367410104</v>
       </c>
       <c r="T37">
-        <v>0.9597101563838929</v>
+        <v>0.9747056275773912</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.278155379487195</v>
+        <v>0.2704288411681062</v>
       </c>
       <c r="W37">
-        <v>0.08561077199281869</v>
+        <v>0.08652713943746261</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9271845982906499</v>
+        <v>0.9014294705603542</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4754,22 +4754,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08747281254891121</v>
+        <v>0.08820081254891121</v>
       </c>
       <c r="C38">
-        <v>2026.582665075105</v>
+        <v>1881.670128963349</v>
       </c>
       <c r="D38">
-        <v>4287.638665075104</v>
+        <v>4214.022128963348</v>
       </c>
       <c r="E38">
-        <v>1126.455999999999</v>
+        <v>1197.752</v>
       </c>
       <c r="F38">
-        <v>2566.655999999999</v>
+        <v>2637.952</v>
       </c>
       <c r="G38">
         <v>305.6</v>
@@ -4790,37 +4790,37 @@
         <v>274.4</v>
       </c>
       <c r="M38">
-        <v>304.4054015999999</v>
+        <v>312.8611072</v>
       </c>
       <c r="N38">
-        <v>-30.00540159999997</v>
+        <v>-38.46110720000001</v>
       </c>
       <c r="O38">
-        <v>-9.001620479999991</v>
+        <v>-11.53833216</v>
       </c>
       <c r="P38">
-        <v>-21.00378111999998</v>
+        <v>-26.92277504000001</v>
       </c>
       <c r="Q38">
-        <v>33.79621888000003</v>
+        <v>27.87722496</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08800475367410104</v>
+        <v>0.08867467039908677</v>
       </c>
       <c r="T38">
-        <v>0.9747056275773911</v>
+        <v>0.990177145475445</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.2704288411681063</v>
+        <v>0.2631199535689682</v>
       </c>
       <c r="W38">
-        <v>0.0865271394374626</v>
+        <v>0.08739397350672037</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9014294705603543</v>
+        <v>0.8770665118965608</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4836,22 +4836,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08820081254891121</v>
+        <v>0.0889288125489112</v>
       </c>
       <c r="C39">
-        <v>1881.670128963349</v>
+        <v>1739.242838102833</v>
       </c>
       <c r="D39">
-        <v>4214.022128963348</v>
+        <v>4142.890838102832</v>
       </c>
       <c r="E39">
-        <v>1197.752</v>
+        <v>1269.048</v>
       </c>
       <c r="F39">
-        <v>2637.952</v>
+        <v>2709.248</v>
       </c>
       <c r="G39">
         <v>305.6</v>
@@ -4872,37 +4872,37 @@
         <v>274.4</v>
       </c>
       <c r="M39">
-        <v>312.8611072</v>
+        <v>321.3168128</v>
       </c>
       <c r="N39">
-        <v>-38.46110720000001</v>
+        <v>-46.91681280000006</v>
       </c>
       <c r="O39">
-        <v>-11.53833216</v>
+        <v>-14.07504384000002</v>
       </c>
       <c r="P39">
-        <v>-26.92277504000001</v>
+        <v>-32.84176896000004</v>
       </c>
       <c r="Q39">
-        <v>27.87722496</v>
+        <v>21.95823103999997</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08867467039908677</v>
+        <v>0.08936619734100754</v>
       </c>
       <c r="T39">
-        <v>0.990177145475445</v>
+        <v>1.006147744596017</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.2631199535689682</v>
+        <v>0.2561957442645217</v>
       </c>
       <c r="W39">
-        <v>0.08739397350672037</v>
+        <v>0.08821518473022773</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8770665118965608</v>
+        <v>0.8539858142150722</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4918,22 +4918,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0889288125489112</v>
+        <v>0.08965681254891121</v>
       </c>
       <c r="C40">
-        <v>1739.242838102833</v>
+        <v>1599.177031205095</v>
       </c>
       <c r="D40">
-        <v>4142.890838102832</v>
+        <v>4074.121031205094</v>
       </c>
       <c r="E40">
-        <v>1269.048</v>
+        <v>1340.344</v>
       </c>
       <c r="F40">
-        <v>2709.248</v>
+        <v>2780.544</v>
       </c>
       <c r="G40">
         <v>305.6</v>
@@ -4954,37 +4954,37 @@
         <v>274.4</v>
       </c>
       <c r="M40">
-        <v>321.3168128</v>
+        <v>329.7725184</v>
       </c>
       <c r="N40">
-        <v>-46.91681280000006</v>
+        <v>-55.37251840000005</v>
       </c>
       <c r="O40">
-        <v>-14.07504384000002</v>
+        <v>-16.61175552000001</v>
       </c>
       <c r="P40">
-        <v>-32.84176896000004</v>
+        <v>-38.76076288000003</v>
       </c>
       <c r="Q40">
-        <v>21.95823103999997</v>
+        <v>16.03923711999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08936619734100754</v>
+        <v>0.09008039729741749</v>
       </c>
       <c r="T40">
-        <v>1.006147744596017</v>
+        <v>1.022641969917263</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.2561957442645217</v>
+        <v>0.2496266226167134</v>
       </c>
       <c r="W40">
-        <v>0.08821518473022773</v>
+        <v>0.0889942825576578</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8539858142150722</v>
+        <v>0.8320887420557115</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5000,22 +5000,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08965681254891121</v>
+        <v>0.09038481254891123</v>
       </c>
       <c r="C41">
-        <v>1599.177031205095</v>
+        <v>1461.357030291922</v>
       </c>
       <c r="D41">
-        <v>4074.121031205094</v>
+        <v>4007.597030291922</v>
       </c>
       <c r="E41">
-        <v>1340.344</v>
+        <v>1411.64</v>
       </c>
       <c r="F41">
-        <v>2780.544</v>
+        <v>2851.84</v>
       </c>
       <c r="G41">
         <v>305.6</v>
@@ -5036,37 +5036,37 @@
         <v>274.4</v>
       </c>
       <c r="M41">
-        <v>329.7725184</v>
+        <v>338.2282240000001</v>
       </c>
       <c r="N41">
-        <v>-55.37251840000005</v>
+        <v>-63.82822400000009</v>
       </c>
       <c r="O41">
-        <v>-16.61175552000001</v>
+        <v>-19.14846720000003</v>
       </c>
       <c r="P41">
-        <v>-38.76076288000003</v>
+        <v>-44.67975680000006</v>
       </c>
       <c r="Q41">
-        <v>16.03923711999998</v>
+        <v>10.12024319999995</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09008039729741749</v>
+        <v>0.09081840391904113</v>
       </c>
       <c r="T41">
-        <v>1.022641969917263</v>
+        <v>1.039686002749217</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.2496266226167134</v>
+        <v>0.2433859570512955</v>
       </c>
       <c r="W41">
-        <v>0.0889942825576578</v>
+        <v>0.08973442549371637</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8320887420557115</v>
+        <v>0.8112865235043185</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5082,22 +5082,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09038481254891123</v>
+        <v>0.1260073929917665</v>
       </c>
       <c r="C42">
-        <v>1461.357030291922</v>
+        <v>-389.8365859886212</v>
       </c>
       <c r="D42">
-        <v>4007.597030291922</v>
+        <v>2227.699414011379</v>
       </c>
       <c r="E42">
-        <v>1411.64</v>
+        <v>1482.936</v>
       </c>
       <c r="F42">
-        <v>2851.84</v>
+        <v>2923.136</v>
       </c>
       <c r="G42">
         <v>305.6</v>
@@ -5118,45 +5118,45 @@
         <v>274.4</v>
       </c>
       <c r="M42">
-        <v>338.2282240000001</v>
+        <v>586.9657088</v>
       </c>
       <c r="N42">
-        <v>-63.82822400000009</v>
+        <v>-312.5657088</v>
       </c>
       <c r="O42">
-        <v>-19.14846720000003</v>
+        <v>-93.76971264000001</v>
       </c>
       <c r="P42">
-        <v>-44.67975680000006</v>
+        <v>-218.79599616</v>
       </c>
       <c r="Q42">
-        <v>10.12024319999995</v>
+        <v>-163.99599616</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09081840391904113</v>
+        <v>0.09360275049877961</v>
       </c>
       <c r="T42">
-        <v>1.039686002749217</v>
+        <v>1.10398961890946</v>
       </c>
       <c r="U42">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.2433859570512955</v>
+        <v>0.1402466937434829</v>
       </c>
       <c r="W42">
-        <v>0.08973442549371637</v>
+        <v>0.1726384638963086</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8112865235043185</v>
+        <v>0.4674889791449431</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5164,22 +5164,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1260073929917665</v>
+        <v>0.1275573929917665</v>
       </c>
       <c r="C43">
-        <v>-389.8365859886212</v>
+        <v>-503.3664924937539</v>
       </c>
       <c r="D43">
-        <v>2227.699414011379</v>
+        <v>2185.465507506246</v>
       </c>
       <c r="E43">
-        <v>1482.936</v>
+        <v>1554.232</v>
       </c>
       <c r="F43">
-        <v>2923.136</v>
+        <v>2994.432</v>
       </c>
       <c r="G43">
         <v>305.6</v>
@@ -5200,37 +5200,37 @@
         <v>274.4</v>
       </c>
       <c r="M43">
-        <v>586.9657088</v>
+        <v>601.2819456000001</v>
       </c>
       <c r="N43">
-        <v>-312.5657088</v>
+        <v>-326.8819456000001</v>
       </c>
       <c r="O43">
-        <v>-93.76971264000001</v>
+        <v>-98.06458368000003</v>
       </c>
       <c r="P43">
-        <v>-218.79599616</v>
+        <v>-228.8173619200001</v>
       </c>
       <c r="Q43">
-        <v>-163.99599616</v>
+        <v>-174.0173619200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09360275049877961</v>
+        <v>0.09442693585220685</v>
       </c>
       <c r="T43">
-        <v>1.10398961890946</v>
+        <v>1.123023922683761</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1402466937434829</v>
+        <v>0.1369074867495905</v>
       </c>
       <c r="W43">
-        <v>0.1726384638963086</v>
+        <v>0.1733089766606822</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4674889791449431</v>
+        <v>0.4563582891653016</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5246,22 +5246,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1275573929917665</v>
+        <v>0.1291073929917665</v>
       </c>
       <c r="C44">
-        <v>-503.366492493753</v>
+        <v>-615.3248084657512</v>
       </c>
       <c r="D44">
-        <v>2185.465507506247</v>
+        <v>2144.803191534249</v>
       </c>
       <c r="E44">
-        <v>1554.232</v>
+        <v>1625.528</v>
       </c>
       <c r="F44">
-        <v>2994.432</v>
+        <v>3065.728</v>
       </c>
       <c r="G44">
         <v>305.6</v>
@@ -5282,37 +5282,37 @@
         <v>274.4</v>
       </c>
       <c r="M44">
-        <v>601.2819456</v>
+        <v>615.5981823999999</v>
       </c>
       <c r="N44">
-        <v>-326.8819456</v>
+        <v>-341.1981824</v>
       </c>
       <c r="O44">
-        <v>-98.06458368</v>
+        <v>-102.35945472</v>
       </c>
       <c r="P44">
-        <v>-228.81736192</v>
+        <v>-238.83872768</v>
       </c>
       <c r="Q44">
-        <v>-174.01736192</v>
+        <v>-184.03872768</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09442693585220685</v>
+        <v>0.09528003998996484</v>
       </c>
       <c r="T44">
-        <v>1.123023922683761</v>
+        <v>1.142726096765932</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1369074867495905</v>
+        <v>0.1337235917089024</v>
       </c>
       <c r="W44">
-        <v>0.1733089766606822</v>
+        <v>0.1739483027848524</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4563582891653016</v>
+        <v>0.4457453056963412</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5328,22 +5328,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1291073929917665</v>
+        <v>0.1306573929917665</v>
       </c>
       <c r="C45">
-        <v>-615.3248084657512</v>
+        <v>-725.7976536370461</v>
       </c>
       <c r="D45">
-        <v>2144.803191534249</v>
+        <v>2105.626346362954</v>
       </c>
       <c r="E45">
-        <v>1625.528</v>
+        <v>1696.824</v>
       </c>
       <c r="F45">
-        <v>3065.728</v>
+        <v>3137.024</v>
       </c>
       <c r="G45">
         <v>305.6</v>
@@ -5364,37 +5364,37 @@
         <v>274.4</v>
       </c>
       <c r="M45">
-        <v>615.5981823999999</v>
+        <v>629.9144192</v>
       </c>
       <c r="N45">
-        <v>-341.1981824</v>
+        <v>-355.5144192</v>
       </c>
       <c r="O45">
-        <v>-102.35945472</v>
+        <v>-106.65432576</v>
       </c>
       <c r="P45">
-        <v>-238.83872768</v>
+        <v>-248.86009344</v>
       </c>
       <c r="Q45">
-        <v>-184.03872768</v>
+        <v>-194.06009344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09528003998996484</v>
+        <v>0.09616361213264282</v>
       </c>
       <c r="T45">
-        <v>1.142726096765932</v>
+        <v>1.163131919922467</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1337235917089024</v>
+        <v>0.1306844191700637</v>
       </c>
       <c r="W45">
-        <v>0.1739483027848524</v>
+        <v>0.1745585686306512</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4457453056963412</v>
+        <v>0.4356147305668788</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5410,22 +5410,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1306573929917665</v>
+        <v>0.1322073929917665</v>
       </c>
       <c r="C46">
-        <v>-725.7976536370461</v>
+        <v>-834.8649683806075</v>
       </c>
       <c r="D46">
-        <v>2105.626346362954</v>
+        <v>2067.855031619392</v>
       </c>
       <c r="E46">
-        <v>1696.824</v>
+        <v>1768.12</v>
       </c>
       <c r="F46">
-        <v>3137.024</v>
+        <v>3208.32</v>
       </c>
       <c r="G46">
         <v>305.6</v>
@@ -5446,37 +5446,37 @@
         <v>274.4</v>
       </c>
       <c r="M46">
-        <v>629.9144192</v>
+        <v>644.230656</v>
       </c>
       <c r="N46">
-        <v>-355.5144192</v>
+        <v>-369.830656</v>
       </c>
       <c r="O46">
-        <v>-106.65432576</v>
+        <v>-110.9491968</v>
       </c>
       <c r="P46">
-        <v>-248.86009344</v>
+        <v>-258.8814592</v>
       </c>
       <c r="Q46">
-        <v>-194.06009344</v>
+        <v>-204.0814592</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09616361213264282</v>
+        <v>0.09707931417141813</v>
       </c>
       <c r="T46">
-        <v>1.163131919922467</v>
+        <v>1.184279773011966</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1306844191700637</v>
+        <v>0.1277803209662845</v>
       </c>
       <c r="W46">
-        <v>0.1745585686306512</v>
+        <v>0.1751417115499701</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4356147305668788</v>
+        <v>0.4259344032209482</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5492,22 +5492,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1322073929917665</v>
+        <v>0.1337573929917665</v>
       </c>
       <c r="C47">
-        <v>-834.8649683806075</v>
+        <v>-942.6010581785176</v>
       </c>
       <c r="D47">
-        <v>2067.855031619392</v>
+        <v>2031.414941821482</v>
       </c>
       <c r="E47">
-        <v>1768.12</v>
+        <v>1839.416</v>
       </c>
       <c r="F47">
-        <v>3208.32</v>
+        <v>3279.616</v>
       </c>
       <c r="G47">
         <v>305.6</v>
@@ -5528,37 +5528,37 @@
         <v>274.4</v>
       </c>
       <c r="M47">
-        <v>644.230656</v>
+        <v>658.5468928</v>
       </c>
       <c r="N47">
-        <v>-369.830656</v>
+        <v>-384.1468928</v>
       </c>
       <c r="O47">
-        <v>-110.9491968</v>
+        <v>-115.24406784</v>
       </c>
       <c r="P47">
-        <v>-258.8814592</v>
+        <v>-268.90282496</v>
       </c>
       <c r="Q47">
-        <v>-204.0814592</v>
+        <v>-214.10282496</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09707931417141813</v>
+        <v>0.09802893110051847</v>
       </c>
       <c r="T47">
-        <v>1.184279773011966</v>
+        <v>1.206210879919595</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1277803209662845</v>
+        <v>0.1250024879018</v>
       </c>
       <c r="W47">
-        <v>0.1751417115499701</v>
+        <v>0.1756995004293186</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4259344032209482</v>
+        <v>0.4166749596726667</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5574,22 +5574,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1337573929917665</v>
+        <v>0.1353073929917665</v>
       </c>
       <c r="C48">
-        <v>-942.6010581785176</v>
+        <v>-1049.075081519147</v>
       </c>
       <c r="D48">
-        <v>2031.414941821482</v>
+        <v>1996.236918480852</v>
       </c>
       <c r="E48">
-        <v>1839.416</v>
+        <v>1910.712</v>
       </c>
       <c r="F48">
-        <v>3279.616</v>
+        <v>3350.912</v>
       </c>
       <c r="G48">
         <v>305.6</v>
@@ -5610,37 +5610,37 @@
         <v>274.4</v>
       </c>
       <c r="M48">
-        <v>658.5468928</v>
+        <v>672.8631296</v>
       </c>
       <c r="N48">
-        <v>-384.1468928</v>
+        <v>-398.4631296</v>
       </c>
       <c r="O48">
-        <v>-115.24406784</v>
+        <v>-119.53893888</v>
       </c>
       <c r="P48">
-        <v>-268.90282496</v>
+        <v>-278.92419072</v>
       </c>
       <c r="Q48">
-        <v>-214.10282496</v>
+        <v>-224.12419072</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09802893110051847</v>
+        <v>0.09901438263071694</v>
       </c>
       <c r="T48">
-        <v>1.206210879919595</v>
+        <v>1.228969575767134</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1250024879018</v>
+        <v>0.1223428604996341</v>
       </c>
       <c r="W48">
-        <v>0.1756995004293186</v>
+        <v>0.1762335536116735</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4166749596726667</v>
+        <v>0.4078095349987803</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5656,22 +5656,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1353073929917665</v>
+        <v>0.1368573929917665</v>
       </c>
       <c r="C49">
-        <v>-1049.075081519147</v>
+        <v>-1154.351487963741</v>
       </c>
       <c r="D49">
-        <v>1996.236918480852</v>
+        <v>1962.256512036259</v>
       </c>
       <c r="E49">
-        <v>1910.712</v>
+        <v>1982.008</v>
       </c>
       <c r="F49">
-        <v>3350.912</v>
+        <v>3422.208</v>
       </c>
       <c r="G49">
         <v>305.6</v>
@@ -5692,37 +5692,37 @@
         <v>274.4</v>
       </c>
       <c r="M49">
-        <v>672.8631296</v>
+        <v>687.1793664</v>
       </c>
       <c r="N49">
-        <v>-398.4631296</v>
+        <v>-412.7793664000001</v>
       </c>
       <c r="O49">
-        <v>-119.53893888</v>
+        <v>-123.83380992</v>
       </c>
       <c r="P49">
-        <v>-278.92419072</v>
+        <v>-288.9455564800001</v>
       </c>
       <c r="Q49">
-        <v>-224.12419072</v>
+        <v>-234.14555648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09901438263071694</v>
+        <v>0.1000377361428461</v>
       </c>
       <c r="T49">
-        <v>1.228969575767134</v>
+        <v>1.252603606070348</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1223428604996341</v>
+        <v>0.1197940509058917</v>
       </c>
       <c r="W49">
-        <v>0.1762335536116735</v>
+        <v>0.176745354578097</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4078095349987803</v>
+        <v>0.399313503019639</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5738,22 +5738,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1368573929917665</v>
+        <v>0.1384073929917665</v>
       </c>
       <c r="C50">
-        <v>-1154.351487963741</v>
+        <v>-1258.490412220626</v>
       </c>
       <c r="D50">
-        <v>1962.256512036259</v>
+        <v>1929.413587779374</v>
       </c>
       <c r="E50">
-        <v>1982.008</v>
+        <v>2053.303999999999</v>
       </c>
       <c r="F50">
-        <v>3422.208</v>
+        <v>3493.503999999999</v>
       </c>
       <c r="G50">
         <v>305.6</v>
@@ -5774,37 +5774,37 @@
         <v>274.4</v>
       </c>
       <c r="M50">
-        <v>687.1793663999999</v>
+        <v>701.4956031999999</v>
       </c>
       <c r="N50">
-        <v>-412.7793664</v>
+        <v>-427.0956031999999</v>
       </c>
       <c r="O50">
-        <v>-123.83380992</v>
+        <v>-128.12868096</v>
       </c>
       <c r="P50">
-        <v>-288.94555648</v>
+        <v>-298.9669222399999</v>
       </c>
       <c r="Q50">
-        <v>-234.14555648</v>
+        <v>-244.1669222399999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1000377361428461</v>
+        <v>0.1011012211652548</v>
       </c>
       <c r="T50">
-        <v>1.252603606070348</v>
+        <v>1.277164461091336</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1197940509058917</v>
+        <v>0.1173492743567919</v>
       </c>
       <c r="W50">
-        <v>0.176745354578097</v>
+        <v>0.1772362657091562</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.399313503019639</v>
+        <v>0.3911642478559729</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5820,22 +5820,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1384073929917665</v>
+        <v>0.1399573929917665</v>
       </c>
       <c r="C51">
-        <v>-1258.490412220626</v>
+        <v>-1361.548029296404</v>
       </c>
       <c r="D51">
-        <v>1929.413587779374</v>
+        <v>1897.651970703595</v>
       </c>
       <c r="E51">
-        <v>2053.303999999999</v>
+        <v>2124.599999999999</v>
       </c>
       <c r="F51">
-        <v>3493.503999999999</v>
+        <v>3564.8</v>
       </c>
       <c r="G51">
         <v>305.6</v>
@@ -5856,37 +5856,37 @@
         <v>274.4</v>
       </c>
       <c r="M51">
-        <v>701.4956031999999</v>
+        <v>715.81184</v>
       </c>
       <c r="N51">
-        <v>-427.0956031999999</v>
+        <v>-441.41184</v>
       </c>
       <c r="O51">
-        <v>-128.12868096</v>
+        <v>-132.423552</v>
       </c>
       <c r="P51">
-        <v>-298.9669222399999</v>
+        <v>-308.988288</v>
       </c>
       <c r="Q51">
-        <v>-244.1669222399999</v>
+        <v>-254.188288</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1011012211652548</v>
+        <v>0.10220724558856</v>
       </c>
       <c r="T51">
-        <v>1.277164461091336</v>
+        <v>1.302707750313162</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1173492743567919</v>
+        <v>0.115002288869656</v>
       </c>
       <c r="W51">
-        <v>0.1772362657091562</v>
+        <v>0.1777075403949731</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3911642478559729</v>
+        <v>0.3833409628988534</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5902,22 +5902,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1399573929917665</v>
+        <v>0.1415073929917665</v>
       </c>
       <c r="C52">
-        <v>-1361.548029296404</v>
+        <v>-1463.57687513668</v>
       </c>
       <c r="D52">
-        <v>1897.651970703595</v>
+        <v>1866.919124863321</v>
       </c>
       <c r="E52">
-        <v>2124.599999999999</v>
+        <v>2195.896</v>
       </c>
       <c r="F52">
-        <v>3564.8</v>
+        <v>3636.096</v>
       </c>
       <c r="G52">
         <v>305.6</v>
@@ -5938,37 +5938,37 @@
         <v>274.4</v>
       </c>
       <c r="M52">
-        <v>715.81184</v>
+        <v>730.1280768</v>
       </c>
       <c r="N52">
-        <v>-441.41184</v>
+        <v>-455.7280768000001</v>
       </c>
       <c r="O52">
-        <v>-132.423552</v>
+        <v>-136.71842304</v>
       </c>
       <c r="P52">
-        <v>-308.988288</v>
+        <v>-319.00965376</v>
       </c>
       <c r="Q52">
-        <v>-254.188288</v>
+        <v>-264.20965376</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.10220724558856</v>
+        <v>0.1033584138658775</v>
       </c>
       <c r="T52">
-        <v>1.302707750313162</v>
+        <v>1.329293622768533</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.115002288869656</v>
+        <v>0.1127473420290745</v>
       </c>
       <c r="W52">
-        <v>0.1777075403949731</v>
+        <v>0.1781603337205618</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3833409628988534</v>
+        <v>0.3758244734302484</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5984,22 +5984,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1415073929917665</v>
+        <v>0.1430573929917665</v>
       </c>
       <c r="C53">
-        <v>-1463.57687513668</v>
+        <v>-1564.626136606304</v>
       </c>
       <c r="D53">
-        <v>1866.919124863321</v>
+        <v>1837.165863393695</v>
       </c>
       <c r="E53">
-        <v>2195.896</v>
+        <v>2267.192</v>
       </c>
       <c r="F53">
-        <v>3636.096</v>
+        <v>3707.392</v>
       </c>
       <c r="G53">
         <v>305.6</v>
@@ -6020,37 +6020,37 @@
         <v>274.4</v>
       </c>
       <c r="M53">
-        <v>730.1280768</v>
+        <v>744.4443136</v>
       </c>
       <c r="N53">
-        <v>-455.7280768000001</v>
+        <v>-470.0443136</v>
       </c>
       <c r="O53">
-        <v>-136.71842304</v>
+        <v>-141.01329408</v>
       </c>
       <c r="P53">
-        <v>-319.00965376</v>
+        <v>-329.03101952</v>
       </c>
       <c r="Q53">
-        <v>-264.20965376</v>
+        <v>-274.23101952</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1033584138658775</v>
+        <v>0.1045575474880833</v>
       </c>
       <c r="T53">
-        <v>1.329293622768533</v>
+        <v>1.356987239909544</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1127473420290745</v>
+        <v>0.1105791239131308</v>
       </c>
       <c r="W53">
-        <v>0.1781603337205618</v>
+        <v>0.1785957119182433</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3758244734302484</v>
+        <v>0.368597079710436</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6066,22 +6066,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1430573929917665</v>
+        <v>0.1446073929917665</v>
       </c>
       <c r="C54">
-        <v>-1564.626136606304</v>
+        <v>-1664.741914175961</v>
       </c>
       <c r="D54">
-        <v>1837.165863393695</v>
+        <v>1808.34608582404</v>
       </c>
       <c r="E54">
-        <v>2267.192</v>
+        <v>2338.488</v>
       </c>
       <c r="F54">
-        <v>3707.392</v>
+        <v>3778.688</v>
       </c>
       <c r="G54">
         <v>305.6</v>
@@ -6102,37 +6102,37 @@
         <v>274.4</v>
       </c>
       <c r="M54">
-        <v>744.4443136</v>
+        <v>758.7605504000001</v>
       </c>
       <c r="N54">
-        <v>-470.0443136</v>
+        <v>-484.3605504000001</v>
       </c>
       <c r="O54">
-        <v>-141.01329408</v>
+        <v>-145.30816512</v>
       </c>
       <c r="P54">
-        <v>-329.03101952</v>
+        <v>-339.0523852800001</v>
       </c>
       <c r="Q54">
-        <v>-274.23101952</v>
+        <v>-284.2523852800001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1045575474880833</v>
+        <v>0.1058077080729361</v>
       </c>
       <c r="T54">
-        <v>1.356987239909544</v>
+        <v>1.38585930884379</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1105791239131308</v>
+        <v>0.1084927253487321</v>
       </c>
       <c r="W54">
-        <v>0.1785957119182433</v>
+        <v>0.1790146607499746</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.368597079710436</v>
+        <v>0.3616424178291069</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6148,22 +6148,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1446073929917665</v>
+        <v>0.1461573929917665</v>
       </c>
       <c r="C55">
-        <v>-1664.741914175961</v>
+        <v>-1763.967460265875</v>
       </c>
       <c r="D55">
-        <v>1808.34608582404</v>
+        <v>1780.416539734125</v>
       </c>
       <c r="E55">
-        <v>2338.488</v>
+        <v>2409.784</v>
       </c>
       <c r="F55">
-        <v>3778.688</v>
+        <v>3849.984</v>
       </c>
       <c r="G55">
         <v>305.6</v>
@@ -6184,37 +6184,37 @@
         <v>274.4</v>
       </c>
       <c r="M55">
-        <v>758.7605504000001</v>
+        <v>773.0767872</v>
       </c>
       <c r="N55">
-        <v>-484.3605504000001</v>
+        <v>-498.6767872</v>
       </c>
       <c r="O55">
-        <v>-145.30816512</v>
+        <v>-149.60303616</v>
       </c>
       <c r="P55">
-        <v>-339.0523852800001</v>
+        <v>-349.07375104</v>
       </c>
       <c r="Q55">
-        <v>-284.2523852800001</v>
+        <v>-294.27375104</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1058077080729361</v>
+        <v>0.107112223465826</v>
       </c>
       <c r="T55">
-        <v>1.38585930884379</v>
+        <v>1.415986685123003</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1084927253487321</v>
+        <v>0.106483600805237</v>
       </c>
       <c r="W55">
-        <v>0.1790146607499746</v>
+        <v>0.1794180929583084</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3616424178291069</v>
+        <v>0.3549453360174568</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6230,22 +6230,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1461573929917665</v>
+        <v>0.1477073929917665</v>
       </c>
       <c r="C56">
-        <v>-1763.967460265875</v>
+        <v>-1862.343395838468</v>
       </c>
       <c r="D56">
-        <v>1780.416539734125</v>
+        <v>1753.336604161532</v>
       </c>
       <c r="E56">
-        <v>2409.784</v>
+        <v>2481.08</v>
       </c>
       <c r="F56">
-        <v>3849.984</v>
+        <v>3921.28</v>
       </c>
       <c r="G56">
         <v>305.6</v>
@@ -6266,37 +6266,37 @@
         <v>274.4</v>
       </c>
       <c r="M56">
-        <v>773.0767872</v>
+        <v>787.3930240000001</v>
       </c>
       <c r="N56">
-        <v>-498.6767872</v>
+        <v>-512.9930240000001</v>
       </c>
       <c r="O56">
-        <v>-149.60303616</v>
+        <v>-153.8979072</v>
       </c>
       <c r="P56">
-        <v>-349.07375104</v>
+        <v>-359.0951168000001</v>
       </c>
       <c r="Q56">
-        <v>-294.27375104</v>
+        <v>-304.2951168000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.107112223465826</v>
+        <v>0.1084747173206222</v>
       </c>
       <c r="T56">
-        <v>1.415986685123003</v>
+        <v>1.447453055903514</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.106483600805237</v>
+        <v>0.1045475353360509</v>
       </c>
       <c r="W56">
-        <v>0.1794180929583084</v>
+        <v>0.179806854904521</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3549453360174568</v>
+        <v>0.348491784453503</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6312,22 +6312,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1477073929917665</v>
+        <v>0.1492573929917665</v>
       </c>
       <c r="C57">
-        <v>-1862.343395838468</v>
+        <v>-1959.907907521017</v>
       </c>
       <c r="D57">
-        <v>1753.336604161532</v>
+        <v>1727.068092478982</v>
       </c>
       <c r="E57">
-        <v>2481.08</v>
+        <v>2552.376</v>
       </c>
       <c r="F57">
-        <v>3921.28</v>
+        <v>3992.576</v>
       </c>
       <c r="G57">
         <v>305.6</v>
@@ -6348,37 +6348,37 @@
         <v>274.4</v>
       </c>
       <c r="M57">
-        <v>787.3930240000001</v>
+        <v>801.7092608</v>
       </c>
       <c r="N57">
-        <v>-512.9930240000001</v>
+        <v>-527.3092608000001</v>
       </c>
       <c r="O57">
-        <v>-153.8979072</v>
+        <v>-158.19277824</v>
       </c>
       <c r="P57">
-        <v>-359.0951168000001</v>
+        <v>-369.11648256</v>
       </c>
       <c r="Q57">
-        <v>-304.2951168000001</v>
+        <v>-314.31648256</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1084747173206222</v>
+        <v>0.1098991427142727</v>
       </c>
       <c r="T57">
-        <v>1.447453055903514</v>
+        <v>1.480349716264957</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1045475353360509</v>
+        <v>0.1026806150621929</v>
       </c>
       <c r="W57">
-        <v>0.179806854904521</v>
+        <v>0.1801817324955117</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.348491784453503</v>
+        <v>0.3422687168739762</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6394,22 +6394,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1492573929917665</v>
+        <v>0.1508073929917665</v>
       </c>
       <c r="C58">
-        <v>-1959.907907521017</v>
+        <v>-2056.696927270135</v>
       </c>
       <c r="D58">
-        <v>1727.068092478982</v>
+        <v>1701.575072729865</v>
       </c>
       <c r="E58">
-        <v>2552.376</v>
+        <v>2623.672</v>
       </c>
       <c r="F58">
-        <v>3992.576</v>
+        <v>4063.872</v>
       </c>
       <c r="G58">
         <v>305.6</v>
@@ -6430,37 +6430,37 @@
         <v>274.4</v>
       </c>
       <c r="M58">
-        <v>801.7092608</v>
+        <v>816.0254976000001</v>
       </c>
       <c r="N58">
-        <v>-527.3092608000001</v>
+        <v>-541.6254976000001</v>
       </c>
       <c r="O58">
-        <v>-158.19277824</v>
+        <v>-162.48764928</v>
       </c>
       <c r="P58">
-        <v>-369.11648256</v>
+        <v>-379.1378483200001</v>
       </c>
       <c r="Q58">
-        <v>-314.31648256</v>
+        <v>-324.3378483200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1098991427142727</v>
+        <v>0.1113898204518139</v>
       </c>
       <c r="T58">
-        <v>1.480349716264957</v>
+        <v>1.514776453852515</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1026806150621929</v>
+        <v>0.1008792007628561</v>
       </c>
       <c r="W58">
-        <v>0.1801817324955117</v>
+        <v>0.1805434564868185</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3422687168739762</v>
+        <v>0.3362640025428538</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6476,22 +6476,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1508073929917665</v>
+        <v>0.1523573929917665</v>
       </c>
       <c r="C59">
-        <v>-2056.696927270135</v>
+        <v>-2152.744296355668</v>
       </c>
       <c r="D59">
-        <v>1701.575072729865</v>
+        <v>1676.823703644333</v>
       </c>
       <c r="E59">
-        <v>2623.672</v>
+        <v>2694.968000000001</v>
       </c>
       <c r="F59">
-        <v>4063.872</v>
+        <v>4135.168000000001</v>
       </c>
       <c r="G59">
         <v>305.6</v>
@@ -6512,37 +6512,37 @@
         <v>274.4</v>
       </c>
       <c r="M59">
-        <v>816.0254976000001</v>
+        <v>830.3417344000002</v>
       </c>
       <c r="N59">
-        <v>-541.6254976000001</v>
+        <v>-555.9417344000002</v>
       </c>
       <c r="O59">
-        <v>-162.48764928</v>
+        <v>-166.7825203200001</v>
       </c>
       <c r="P59">
-        <v>-379.1378483200001</v>
+        <v>-389.1592140800001</v>
       </c>
       <c r="Q59">
-        <v>-324.3378483200001</v>
+        <v>-334.3592140800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1113898204518139</v>
+        <v>0.1129514828435237</v>
       </c>
       <c r="T59">
-        <v>1.514776453852515</v>
+        <v>1.550842559896622</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1008792007628561</v>
+        <v>0.0991399041979793</v>
       </c>
       <c r="W59">
-        <v>0.1805434564868185</v>
+        <v>0.1808927072370458</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3362640025428538</v>
+        <v>0.3304663473265976</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6558,22 +6558,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1523573929917665</v>
+        <v>0.1539073929917665</v>
       </c>
       <c r="C60">
-        <v>-2152.744296355666</v>
+        <v>-2248.081915237796</v>
       </c>
       <c r="D60">
-        <v>1676.823703644334</v>
+        <v>1652.782084762203</v>
       </c>
       <c r="E60">
-        <v>2694.968</v>
+        <v>2766.263999999999</v>
       </c>
       <c r="F60">
-        <v>4135.168</v>
+        <v>4206.463999999999</v>
       </c>
       <c r="G60">
         <v>305.6</v>
@@ -6594,37 +6594,37 @@
         <v>274.4</v>
       </c>
       <c r="M60">
-        <v>830.3417344</v>
+        <v>844.6579711999998</v>
       </c>
       <c r="N60">
-        <v>-555.9417344</v>
+        <v>-570.2579711999998</v>
       </c>
       <c r="O60">
-        <v>-166.78252032</v>
+        <v>-171.07739136</v>
       </c>
       <c r="P60">
-        <v>-389.15921408</v>
+        <v>-399.1805798399998</v>
       </c>
       <c r="Q60">
-        <v>-334.35921408</v>
+        <v>-344.3805798399998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1129514828435237</v>
+        <v>0.1145893238884877</v>
       </c>
       <c r="T60">
-        <v>1.550842559896622</v>
+        <v>1.588667988186783</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.09913990419797931</v>
+        <v>0.09745956683869157</v>
       </c>
       <c r="W60">
-        <v>0.1808927072370458</v>
+        <v>0.1812301189787907</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3304663473265977</v>
+        <v>0.3248652227956386</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6640,22 +6640,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1539073929917665</v>
+        <v>0.1554573929917665</v>
       </c>
       <c r="C61">
-        <v>-2248.081915237796</v>
+        <v>-2342.739880733125</v>
       </c>
       <c r="D61">
-        <v>1652.782084762203</v>
+        <v>1629.420119266874</v>
       </c>
       <c r="E61">
-        <v>2766.263999999999</v>
+        <v>2837.559999999999</v>
       </c>
       <c r="F61">
-        <v>4206.463999999999</v>
+        <v>4277.759999999999</v>
       </c>
       <c r="G61">
         <v>305.6</v>
@@ -6676,37 +6676,37 @@
         <v>274.4</v>
       </c>
       <c r="M61">
-        <v>844.6579711999998</v>
+        <v>858.9742079999999</v>
       </c>
       <c r="N61">
-        <v>-570.2579711999998</v>
+        <v>-584.5742079999999</v>
       </c>
       <c r="O61">
-        <v>-171.07739136</v>
+        <v>-175.3722624</v>
       </c>
       <c r="P61">
-        <v>-399.1805798399998</v>
+        <v>-409.2019455999999</v>
       </c>
       <c r="Q61">
-        <v>-344.3805798399998</v>
+        <v>-354.4019455999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1145893238884877</v>
+        <v>0.1163090569856999</v>
       </c>
       <c r="T61">
-        <v>1.588667988186783</v>
+        <v>1.628384687891453</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.09745956683869157</v>
+        <v>0.09583524072471336</v>
       </c>
       <c r="W61">
-        <v>0.1812301189787907</v>
+        <v>0.1815562836624776</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3248652227956386</v>
+        <v>0.3194508024157112</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6722,22 +6722,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1554573929917665</v>
+        <v>0.1570073929917665</v>
       </c>
       <c r="C62">
-        <v>-2342.739880733125</v>
+        <v>-2436.746611709893</v>
       </c>
       <c r="D62">
-        <v>1629.420119266874</v>
+        <v>1606.709388290106</v>
       </c>
       <c r="E62">
-        <v>2837.559999999999</v>
+        <v>2908.856</v>
       </c>
       <c r="F62">
-        <v>4277.759999999999</v>
+        <v>4349.056</v>
       </c>
       <c r="G62">
         <v>305.6</v>
@@ -6758,37 +6758,37 @@
         <v>274.4</v>
       </c>
       <c r="M62">
-        <v>858.9742079999999</v>
+        <v>873.2904447999999</v>
       </c>
       <c r="N62">
-        <v>-584.5742079999999</v>
+        <v>-598.8904448</v>
       </c>
       <c r="O62">
-        <v>-175.3722624</v>
+        <v>-179.66713344</v>
       </c>
       <c r="P62">
-        <v>-409.2019455999999</v>
+        <v>-419.22331136</v>
       </c>
       <c r="Q62">
-        <v>-354.4019455999999</v>
+        <v>-364.42331136</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1163090569856999</v>
+        <v>0.1181169815237948</v>
       </c>
       <c r="T62">
-        <v>1.628384687891453</v>
+        <v>1.670138141427131</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.09583524072471336</v>
+        <v>0.09426417120463608</v>
       </c>
       <c r="W62">
-        <v>0.1815562836624776</v>
+        <v>0.1818717544221091</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3194508024157112</v>
+        <v>0.3142139040154536</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6804,22 +6804,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1570073929917665</v>
+        <v>0.1585573929917665</v>
       </c>
       <c r="C63">
-        <v>-2436.746611709893</v>
+        <v>-2530.128964416111</v>
       </c>
       <c r="D63">
-        <v>1606.709388290106</v>
+        <v>1584.623035583889</v>
       </c>
       <c r="E63">
-        <v>2908.856</v>
+        <v>2980.152</v>
       </c>
       <c r="F63">
-        <v>4349.056</v>
+        <v>4420.352</v>
       </c>
       <c r="G63">
         <v>305.6</v>
@@ -6840,37 +6840,37 @@
         <v>274.4</v>
       </c>
       <c r="M63">
-        <v>873.2904447999999</v>
+        <v>887.6066816</v>
       </c>
       <c r="N63">
-        <v>-598.8904448</v>
+        <v>-613.2066816</v>
       </c>
       <c r="O63">
-        <v>-179.66713344</v>
+        <v>-183.96200448</v>
       </c>
       <c r="P63">
-        <v>-419.22331136</v>
+        <v>-429.24467712</v>
       </c>
       <c r="Q63">
-        <v>-364.42331136</v>
+        <v>-374.44467712</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1181169815237948</v>
+        <v>0.1200200599849473</v>
       </c>
       <c r="T63">
-        <v>1.670138141427131</v>
+        <v>1.714089145148898</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.09426417120463608</v>
+        <v>0.09274378134649679</v>
       </c>
       <c r="W63">
-        <v>0.1818717544221091</v>
+        <v>0.1821770487056235</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3142139040154536</v>
+        <v>0.309145937821656</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6886,22 +6886,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1585573929917665</v>
+        <v>0.1601073929917665</v>
       </c>
       <c r="C64">
-        <v>-2530.128964416111</v>
+        <v>-2622.912338424649</v>
       </c>
       <c r="D64">
-        <v>1584.623035583889</v>
+        <v>1563.135661575351</v>
       </c>
       <c r="E64">
-        <v>2980.152</v>
+        <v>3051.448</v>
       </c>
       <c r="F64">
-        <v>4420.352</v>
+        <v>4491.648</v>
       </c>
       <c r="G64">
         <v>305.6</v>
@@ -6922,37 +6922,37 @@
         <v>274.4</v>
       </c>
       <c r="M64">
-        <v>887.6066816</v>
+        <v>901.9229184000001</v>
       </c>
       <c r="N64">
-        <v>-613.2066816</v>
+        <v>-627.5229184000001</v>
       </c>
       <c r="O64">
-        <v>-183.96200448</v>
+        <v>-188.25687552</v>
       </c>
       <c r="P64">
-        <v>-429.24467712</v>
+        <v>-439.2660428800001</v>
       </c>
       <c r="Q64">
-        <v>-374.44467712</v>
+        <v>-384.4660428800001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1200200599849473</v>
+        <v>0.122026007552108</v>
       </c>
       <c r="T64">
-        <v>1.714089145148898</v>
+        <v>1.760415878801571</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.09274378134649679</v>
+        <v>0.09127165783306032</v>
       </c>
       <c r="W64">
-        <v>0.1821770487056235</v>
+        <v>0.1824726511071215</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.309145937821656</v>
+        <v>0.3042388594435345</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6968,22 +6968,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1601073929917665</v>
+        <v>0.1616573929917665</v>
       </c>
       <c r="C65">
-        <v>-2622.912338424649</v>
+        <v>-2715.120774073998</v>
       </c>
       <c r="D65">
-        <v>1563.135661575351</v>
+        <v>1542.223225926001</v>
       </c>
       <c r="E65">
-        <v>3051.448</v>
+        <v>3122.744</v>
       </c>
       <c r="F65">
-        <v>4491.648</v>
+        <v>4562.944</v>
       </c>
       <c r="G65">
         <v>305.6</v>
@@ -7004,37 +7004,37 @@
         <v>274.4</v>
       </c>
       <c r="M65">
-        <v>901.9229184000001</v>
+        <v>916.2391551999999</v>
       </c>
       <c r="N65">
-        <v>-627.5229184000001</v>
+        <v>-641.8391551999999</v>
       </c>
       <c r="O65">
-        <v>-188.25687552</v>
+        <v>-192.55174656</v>
       </c>
       <c r="P65">
-        <v>-439.2660428800001</v>
+        <v>-449.28740864</v>
       </c>
       <c r="Q65">
-        <v>-384.4660428800001</v>
+        <v>-394.48740864</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.122026007552108</v>
+        <v>0.1241433966507777</v>
       </c>
       <c r="T65">
-        <v>1.760415878801571</v>
+        <v>1.809316319879392</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09127165783306032</v>
+        <v>0.08984553817941877</v>
       </c>
       <c r="W65">
-        <v>0.1824726511071215</v>
+        <v>0.1827590159335727</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3042388594435345</v>
+        <v>0.2994851272647292</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7050,22 +7050,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1616573929917665</v>
+        <v>0.1632073929917665</v>
       </c>
       <c r="C66">
-        <v>-2715.120774073998</v>
+        <v>-2806.777042190615</v>
       </c>
       <c r="D66">
-        <v>1542.223225926001</v>
+        <v>1521.862957809385</v>
       </c>
       <c r="E66">
-        <v>3122.744</v>
+        <v>3194.04</v>
       </c>
       <c r="F66">
-        <v>4562.944</v>
+        <v>4634.24</v>
       </c>
       <c r="G66">
         <v>305.6</v>
@@ -7086,37 +7086,37 @@
         <v>274.4</v>
       </c>
       <c r="M66">
-        <v>916.2391551999999</v>
+        <v>930.555392</v>
       </c>
       <c r="N66">
-        <v>-641.8391551999999</v>
+        <v>-656.155392</v>
       </c>
       <c r="O66">
-        <v>-192.55174656</v>
+        <v>-196.8466176</v>
       </c>
       <c r="P66">
-        <v>-449.28740864</v>
+        <v>-459.3087744</v>
       </c>
       <c r="Q66">
-        <v>-394.48740864</v>
+        <v>-404.5087744</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1241433966507777</v>
+        <v>0.1263817794122285</v>
       </c>
       <c r="T66">
-        <v>1.809316319879392</v>
+        <v>1.861011071875946</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08984553817941877</v>
+        <v>0.08846329913050463</v>
       </c>
       <c r="W66">
-        <v>0.1827590159335727</v>
+        <v>0.1830365695345947</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2994851272647292</v>
+        <v>0.2948776637683488</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7132,22 +7132,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1632073929917665</v>
+        <v>0.1647573929917665</v>
       </c>
       <c r="C67">
-        <v>-2806.777042190615</v>
+        <v>-2897.902726796832</v>
       </c>
       <c r="D67">
-        <v>1521.862957809385</v>
+        <v>1502.033273203168</v>
       </c>
       <c r="E67">
-        <v>3194.04</v>
+        <v>3265.336</v>
       </c>
       <c r="F67">
-        <v>4634.24</v>
+        <v>4705.536</v>
       </c>
       <c r="G67">
         <v>305.6</v>
@@ -7168,37 +7168,37 @@
         <v>274.4</v>
       </c>
       <c r="M67">
-        <v>930.555392</v>
+        <v>944.8716288000001</v>
       </c>
       <c r="N67">
-        <v>-656.155392</v>
+        <v>-670.4716288000001</v>
       </c>
       <c r="O67">
-        <v>-196.8466176</v>
+        <v>-201.14148864</v>
       </c>
       <c r="P67">
-        <v>-459.3087744</v>
+        <v>-469.33014016</v>
       </c>
       <c r="Q67">
-        <v>-404.5087744</v>
+        <v>-414.53014016</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1263817794122285</v>
+        <v>0.1287518317478823</v>
       </c>
       <c r="T67">
-        <v>1.861011071875946</v>
+        <v>1.915746691637003</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08846329913050463</v>
+        <v>0.08712294611337577</v>
       </c>
       <c r="W67">
-        <v>0.1830365695345947</v>
+        <v>0.1833057124204341</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2948776637683488</v>
+        <v>0.2904098203779192</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7214,22 +7214,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1647573929917665</v>
+        <v>0.1663073929917665</v>
       </c>
       <c r="C68">
-        <v>-2897.902726796832</v>
+        <v>-2988.518301435909</v>
       </c>
       <c r="D68">
-        <v>1502.033273203168</v>
+        <v>1482.713698564092</v>
       </c>
       <c r="E68">
-        <v>3265.336</v>
+        <v>3336.632000000001</v>
       </c>
       <c r="F68">
-        <v>4705.536</v>
+        <v>4776.832</v>
       </c>
       <c r="G68">
         <v>305.6</v>
@@ -7250,37 +7250,37 @@
         <v>274.4</v>
       </c>
       <c r="M68">
-        <v>944.8716288000001</v>
+        <v>959.1878656000001</v>
       </c>
       <c r="N68">
-        <v>-670.4716288000001</v>
+        <v>-684.7878656000001</v>
       </c>
       <c r="O68">
-        <v>-201.14148864</v>
+        <v>-205.43635968</v>
       </c>
       <c r="P68">
-        <v>-469.33014016</v>
+        <v>-479.3515059200001</v>
       </c>
       <c r="Q68">
-        <v>-414.53014016</v>
+        <v>-424.5515059200001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1287518317478823</v>
+        <v>0.1312655236190302</v>
       </c>
       <c r="T68">
-        <v>1.915746691637003</v>
+        <v>1.97379962168661</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08712294611337577</v>
+        <v>0.08582260363407164</v>
       </c>
       <c r="W68">
-        <v>0.1833057124204341</v>
+        <v>0.1835668211902784</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2904098203779192</v>
+        <v>0.2860753454469055</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7296,22 +7296,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1663073929917665</v>
+        <v>0.1678573929917665</v>
       </c>
       <c r="C69">
-        <v>-2988.518301435909</v>
+        <v>-3078.643199681583</v>
       </c>
       <c r="D69">
-        <v>1482.713698564092</v>
+        <v>1463.884800318417</v>
       </c>
       <c r="E69">
-        <v>3336.632000000001</v>
+        <v>3407.928</v>
       </c>
       <c r="F69">
-        <v>4776.832</v>
+        <v>4848.128</v>
       </c>
       <c r="G69">
         <v>305.6</v>
@@ -7332,37 +7332,37 @@
         <v>274.4</v>
       </c>
       <c r="M69">
-        <v>959.1878656000001</v>
+        <v>973.5041024</v>
       </c>
       <c r="N69">
-        <v>-684.7878656000001</v>
+        <v>-699.1041024</v>
       </c>
       <c r="O69">
-        <v>-205.43635968</v>
+        <v>-209.73123072</v>
       </c>
       <c r="P69">
-        <v>-479.3515059200001</v>
+        <v>-489.37287168</v>
       </c>
       <c r="Q69">
-        <v>-424.5515059200001</v>
+        <v>-434.57287168</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1312655236190302</v>
+        <v>0.1339363212321249</v>
       </c>
       <c r="T69">
-        <v>1.97379962168661</v>
+        <v>2.035480859864316</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08582260363407164</v>
+        <v>0.0845605065218059</v>
       </c>
       <c r="W69">
-        <v>0.1835668211902784</v>
+        <v>0.1838202502904214</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2860753454469055</v>
+        <v>0.2818683550726864</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7378,22 +7378,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1678573929917665</v>
+        <v>0.1694073929917665</v>
       </c>
       <c r="C70">
-        <v>-3078.643199681583</v>
+        <v>-3168.295880342623</v>
       </c>
       <c r="D70">
-        <v>1463.884800318417</v>
+        <v>1445.528119657377</v>
       </c>
       <c r="E70">
-        <v>3407.928</v>
+        <v>3479.224</v>
       </c>
       <c r="F70">
-        <v>4848.128</v>
+        <v>4919.424</v>
       </c>
       <c r="G70">
         <v>305.6</v>
@@ -7414,37 +7414,37 @@
         <v>274.4</v>
       </c>
       <c r="M70">
-        <v>973.5041024</v>
+        <v>987.8203392</v>
       </c>
       <c r="N70">
-        <v>-699.1041024</v>
+        <v>-713.4203392000001</v>
       </c>
       <c r="O70">
-        <v>-209.73123072</v>
+        <v>-214.02610176</v>
       </c>
       <c r="P70">
-        <v>-489.37287168</v>
+        <v>-499.39423744</v>
       </c>
       <c r="Q70">
-        <v>-434.57287168</v>
+        <v>-444.59423744</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1339363212321249</v>
+        <v>0.1367794283686451</v>
       </c>
       <c r="T70">
-        <v>2.035480859864316</v>
+        <v>2.101141532763165</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.0845605065218059</v>
+        <v>0.08333499193453334</v>
       </c>
       <c r="W70">
-        <v>0.1838202502904214</v>
+        <v>0.1840663336195457</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2818683550726864</v>
+        <v>0.2777833064484445</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7460,22 +7460,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1694073929917665</v>
+        <v>0.1709573929917665</v>
       </c>
       <c r="C71">
-        <v>-3168.295880342623</v>
+        <v>-3257.493887822248</v>
       </c>
       <c r="D71">
-        <v>1445.528119657377</v>
+        <v>1427.626112177752</v>
       </c>
       <c r="E71">
-        <v>3479.224</v>
+        <v>3550.52</v>
       </c>
       <c r="F71">
-        <v>4919.424</v>
+        <v>4990.72</v>
       </c>
       <c r="G71">
         <v>305.6</v>
@@ -7496,37 +7496,37 @@
         <v>274.4</v>
       </c>
       <c r="M71">
-        <v>987.8203392</v>
+        <v>1002.136576</v>
       </c>
       <c r="N71">
-        <v>-713.4203392000001</v>
+        <v>-727.7365760000001</v>
       </c>
       <c r="O71">
-        <v>-214.02610176</v>
+        <v>-218.3209728</v>
       </c>
       <c r="P71">
-        <v>-499.39423744</v>
+        <v>-509.4156032000001</v>
       </c>
       <c r="Q71">
-        <v>-444.59423744</v>
+        <v>-454.6156032000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1367794283686451</v>
+        <v>0.1398120759809333</v>
       </c>
       <c r="T71">
-        <v>2.101141532763165</v>
+        <v>2.171179583855271</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08333499193453334</v>
+        <v>0.08214449204975428</v>
       </c>
       <c r="W71">
-        <v>0.1840663336195457</v>
+        <v>0.1843053859964094</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2777833064484445</v>
+        <v>0.2738149734991809</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7542,22 +7542,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1709573929917665</v>
+        <v>0.1725073929917665</v>
       </c>
       <c r="C72">
-        <v>-3257.493887822248</v>
+        <v>-3346.25390804733</v>
       </c>
       <c r="D72">
-        <v>1427.626112177752</v>
+        <v>1410.16209195267</v>
       </c>
       <c r="E72">
-        <v>3550.52</v>
+        <v>3621.816000000001</v>
       </c>
       <c r="F72">
-        <v>4990.72</v>
+        <v>5062.016000000001</v>
       </c>
       <c r="G72">
         <v>305.6</v>
@@ -7578,37 +7578,37 @@
         <v>274.4</v>
       </c>
       <c r="M72">
-        <v>1002.136576</v>
+        <v>1016.4528128</v>
       </c>
       <c r="N72">
-        <v>-727.7365760000001</v>
+        <v>-742.0528128000002</v>
       </c>
       <c r="O72">
-        <v>-218.3209728</v>
+        <v>-222.6158438400001</v>
       </c>
       <c r="P72">
-        <v>-509.4156032000001</v>
+        <v>-519.4369689600002</v>
       </c>
       <c r="Q72">
-        <v>-454.6156032000001</v>
+        <v>-464.6369689600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1398120759809333</v>
+        <v>0.1430538717044137</v>
       </c>
       <c r="T72">
-        <v>2.171179583855271</v>
+        <v>2.246047845367522</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08214449204975428</v>
+        <v>0.08098752737299718</v>
       </c>
       <c r="W72">
-        <v>0.1843053859964094</v>
+        <v>0.1845377045035022</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2738149734991809</v>
+        <v>0.2699584245766573</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7624,22 +7624,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1725073929917665</v>
+        <v>0.1740573929917665</v>
       </c>
       <c r="C73">
-        <v>-3346.253908047329</v>
+        <v>-3434.591820342139</v>
       </c>
       <c r="D73">
-        <v>1410.16209195267</v>
+        <v>1393.12017965786</v>
       </c>
       <c r="E73">
-        <v>3621.816</v>
+        <v>3693.111999999999</v>
       </c>
       <c r="F73">
-        <v>5062.016</v>
+        <v>5133.311999999999</v>
       </c>
       <c r="G73">
         <v>305.6</v>
@@ -7660,37 +7660,37 @@
         <v>274.4</v>
       </c>
       <c r="M73">
-        <v>1016.4528128</v>
+        <v>1030.7690496</v>
       </c>
       <c r="N73">
-        <v>-742.0528128</v>
+        <v>-756.3690495999998</v>
       </c>
       <c r="O73">
-        <v>-222.61584384</v>
+        <v>-226.9107148799999</v>
       </c>
       <c r="P73">
-        <v>-519.4369689599999</v>
+        <v>-529.4583347199998</v>
       </c>
       <c r="Q73">
-        <v>-464.6369689599999</v>
+        <v>-474.6583347199998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1430538717044137</v>
+        <v>0.1465272242652856</v>
       </c>
       <c r="T73">
-        <v>2.246047845367521</v>
+        <v>2.326263839844933</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08098752737299719</v>
+        <v>0.07986270060392779</v>
       </c>
       <c r="W73">
-        <v>0.1845377045035022</v>
+        <v>0.1847635697187313</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2699584245766573</v>
+        <v>0.2662090020130927</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7706,22 +7706,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1740573929917665</v>
+        <v>0.1756073929917665</v>
       </c>
       <c r="C74">
-        <v>-3434.591820342139</v>
+        <v>-3522.522745585623</v>
       </c>
       <c r="D74">
-        <v>1393.12017965786</v>
+        <v>1376.485254414376</v>
       </c>
       <c r="E74">
-        <v>3693.111999999999</v>
+        <v>3764.407999999999</v>
       </c>
       <c r="F74">
-        <v>5133.311999999999</v>
+        <v>5204.607999999999</v>
       </c>
       <c r="G74">
         <v>305.6</v>
@@ -7742,37 +7742,37 @@
         <v>274.4</v>
       </c>
       <c r="M74">
-        <v>1030.7690496</v>
+        <v>1045.0852864</v>
       </c>
       <c r="N74">
-        <v>-756.3690495999998</v>
+        <v>-770.6852863999999</v>
       </c>
       <c r="O74">
-        <v>-226.9107148799999</v>
+        <v>-231.2055859199999</v>
       </c>
       <c r="P74">
-        <v>-529.4583347199998</v>
+        <v>-539.4797004799999</v>
       </c>
       <c r="Q74">
-        <v>-474.6583347199998</v>
+        <v>-484.6797004799999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1465272242652856</v>
+        <v>0.1502578622010369</v>
       </c>
       <c r="T74">
-        <v>2.326263839844933</v>
+        <v>2.412421759839189</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07986270060392779</v>
+        <v>0.07876869100661371</v>
       </c>
       <c r="W74">
-        <v>0.1847635697187313</v>
+        <v>0.184983246845872</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2662090020130927</v>
+        <v>0.2625623033553791</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7788,22 +7788,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1756073929917665</v>
+        <v>0.1771573929917665</v>
       </c>
       <c r="C75">
-        <v>-3522.522745585623</v>
+        <v>-3610.06109095918</v>
       </c>
       <c r="D75">
-        <v>1376.485254414376</v>
+        <v>1360.242909040819</v>
       </c>
       <c r="E75">
-        <v>3764.407999999999</v>
+        <v>3835.704</v>
       </c>
       <c r="F75">
-        <v>5204.607999999999</v>
+        <v>5275.904</v>
       </c>
       <c r="G75">
         <v>305.6</v>
@@ -7824,37 +7824,37 @@
         <v>274.4</v>
       </c>
       <c r="M75">
-        <v>1045.0852864</v>
+        <v>1059.4015232</v>
       </c>
       <c r="N75">
-        <v>-770.6852863999999</v>
+        <v>-785.0015232</v>
       </c>
       <c r="O75">
-        <v>-231.2055859199999</v>
+        <v>-235.50045696</v>
       </c>
       <c r="P75">
-        <v>-539.4797004799999</v>
+        <v>-549.50106624</v>
       </c>
       <c r="Q75">
-        <v>-484.6797004799999</v>
+        <v>-494.70106624</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1502578622010369</v>
+        <v>0.1542754722856922</v>
       </c>
       <c r="T75">
-        <v>2.412421759839189</v>
+        <v>2.505207212140697</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.07876869100661371</v>
+        <v>0.07770424923625406</v>
       </c>
       <c r="W75">
-        <v>0.184983246845872</v>
+        <v>0.1851969867533602</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2625623033553791</v>
+        <v>0.2590141641208469</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7870,22 +7870,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1771573929917665</v>
+        <v>0.1787073929917665</v>
       </c>
       <c r="C76">
-        <v>-3610.06109095918</v>
+        <v>-3697.220591563274</v>
       </c>
       <c r="D76">
-        <v>1360.242909040819</v>
+        <v>1344.379408436726</v>
       </c>
       <c r="E76">
-        <v>3835.704</v>
+        <v>3907</v>
       </c>
       <c r="F76">
-        <v>5275.904</v>
+        <v>5347.2</v>
       </c>
       <c r="G76">
         <v>305.6</v>
@@ -7906,37 +7906,37 @@
         <v>274.4</v>
       </c>
       <c r="M76">
-        <v>1059.4015232</v>
+        <v>1073.71776</v>
       </c>
       <c r="N76">
-        <v>-785.0015232</v>
+        <v>-799.31776</v>
       </c>
       <c r="O76">
-        <v>-235.50045696</v>
+        <v>-239.795328</v>
       </c>
       <c r="P76">
-        <v>-549.50106624</v>
+        <v>-559.522432</v>
       </c>
       <c r="Q76">
-        <v>-494.70106624</v>
+        <v>-504.722432</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1542754722856922</v>
+        <v>0.1586144911771199</v>
       </c>
       <c r="T76">
-        <v>2.505207212140697</v>
+        <v>2.605415500626325</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.07770424923625406</v>
+        <v>0.07666819257977069</v>
       </c>
       <c r="W76">
-        <v>0.1851969867533602</v>
+        <v>0.1854050269299821</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2590141641208469</v>
+        <v>0.2555606419325689</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7952,22 +7952,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1787073929917665</v>
+        <v>0.1802573929917665</v>
       </c>
       <c r="C77">
-        <v>-3697.220591563274</v>
+        <v>-3784.014349155558</v>
       </c>
       <c r="D77">
-        <v>1344.379408436726</v>
+        <v>1328.881650844442</v>
       </c>
       <c r="E77">
-        <v>3907</v>
+        <v>3978.296</v>
       </c>
       <c r="F77">
-        <v>5347.2</v>
+        <v>5418.496</v>
       </c>
       <c r="G77">
         <v>305.6</v>
@@ -7988,37 +7988,37 @@
         <v>274.4</v>
       </c>
       <c r="M77">
-        <v>1073.71776</v>
+        <v>1088.0339968</v>
       </c>
       <c r="N77">
-        <v>-799.31776</v>
+        <v>-813.6339968000001</v>
       </c>
       <c r="O77">
-        <v>-239.795328</v>
+        <v>-244.09019904</v>
       </c>
       <c r="P77">
-        <v>-559.522432</v>
+        <v>-569.5437977600001</v>
       </c>
       <c r="Q77">
-        <v>-504.722432</v>
+        <v>-514.74379776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1586144911771199</v>
+        <v>0.1633150949761666</v>
       </c>
       <c r="T77">
-        <v>2.605415500626325</v>
+        <v>2.713974479819088</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07666819257977069</v>
+        <v>0.07565940057214211</v>
       </c>
       <c r="W77">
-        <v>0.1854050269299821</v>
+        <v>0.1856075923651139</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2555606419325689</v>
+        <v>0.2521980019071404</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8034,22 +8034,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1802573929917665</v>
+        <v>0.1818073929917665</v>
       </c>
       <c r="C78">
-        <v>-3784.014349155558</v>
+        <v>-3870.454868240146</v>
       </c>
       <c r="D78">
-        <v>1328.881650844442</v>
+        <v>1313.737131759854</v>
       </c>
       <c r="E78">
-        <v>3978.296</v>
+        <v>4049.592</v>
       </c>
       <c r="F78">
-        <v>5418.496</v>
+        <v>5489.791999999999</v>
       </c>
       <c r="G78">
         <v>305.6</v>
@@ -8070,37 +8070,37 @@
         <v>274.4</v>
       </c>
       <c r="M78">
-        <v>1088.0339968</v>
+        <v>1102.3502336</v>
       </c>
       <c r="N78">
-        <v>-813.6339968000001</v>
+        <v>-827.9502335999999</v>
       </c>
       <c r="O78">
-        <v>-244.09019904</v>
+        <v>-248.38507008</v>
       </c>
       <c r="P78">
-        <v>-569.5437977600001</v>
+        <v>-579.5651635199999</v>
       </c>
       <c r="Q78">
-        <v>-514.74379776</v>
+        <v>-524.76516352</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1633150949761666</v>
+        <v>0.168424446931652</v>
       </c>
       <c r="T78">
-        <v>2.713974479819088</v>
+        <v>2.831973370246005</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07565940057214211</v>
+        <v>0.07467681095432209</v>
       </c>
       <c r="W78">
-        <v>0.1856075923651139</v>
+        <v>0.1858048963603721</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2521980019071404</v>
+        <v>0.2489227031810737</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8116,22 +8116,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1818073929917665</v>
+        <v>0.1833573929917665</v>
       </c>
       <c r="C79">
-        <v>-3870.454868240146</v>
+        <v>-3956.554089716941</v>
       </c>
       <c r="D79">
-        <v>1313.737131759854</v>
+        <v>1298.933910283058</v>
       </c>
       <c r="E79">
-        <v>4049.592</v>
+        <v>4120.888</v>
       </c>
       <c r="F79">
-        <v>5489.791999999999</v>
+        <v>5561.088</v>
       </c>
       <c r="G79">
         <v>305.6</v>
@@ -8152,37 +8152,37 @@
         <v>274.4</v>
       </c>
       <c r="M79">
-        <v>1102.3502336</v>
+        <v>1116.6664704</v>
       </c>
       <c r="N79">
-        <v>-827.9502335999999</v>
+        <v>-842.2664704</v>
       </c>
       <c r="O79">
-        <v>-248.38507008</v>
+        <v>-252.67994112</v>
       </c>
       <c r="P79">
-        <v>-579.5651635199999</v>
+        <v>-589.58652928</v>
       </c>
       <c r="Q79">
-        <v>-524.76516352</v>
+        <v>-534.78652928</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.168424446931652</v>
+        <v>0.1739982854285454</v>
       </c>
       <c r="T79">
-        <v>2.831973370246005</v>
+        <v>2.960699432529915</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07467681095432209</v>
+        <v>0.07371941594208718</v>
       </c>
       <c r="W79">
-        <v>0.1858048963603721</v>
+        <v>0.1859971412788289</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2489227031810737</v>
+        <v>0.245731386473624</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8198,22 +8198,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1833573929917665</v>
+        <v>0.1849073929917665</v>
       </c>
       <c r="C80">
-        <v>-3956.554089716941</v>
+        <v>-4042.323422281358</v>
       </c>
       <c r="D80">
-        <v>1298.933910283058</v>
+        <v>1284.460577718643</v>
       </c>
       <c r="E80">
-        <v>4120.888</v>
+        <v>4192.184</v>
       </c>
       <c r="F80">
-        <v>5561.088</v>
+        <v>5632.384</v>
       </c>
       <c r="G80">
         <v>305.6</v>
@@ -8234,37 +8234,37 @@
         <v>274.4</v>
       </c>
       <c r="M80">
-        <v>1116.6664704</v>
+        <v>1130.9827072</v>
       </c>
       <c r="N80">
-        <v>-842.2664704</v>
+        <v>-856.5827072000001</v>
       </c>
       <c r="O80">
-        <v>-252.67994112</v>
+        <v>-256.97481216</v>
       </c>
       <c r="P80">
-        <v>-589.58652928</v>
+        <v>-599.6078950400001</v>
       </c>
       <c r="Q80">
-        <v>-534.78652928</v>
+        <v>-544.8078950400002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1739982854285454</v>
+        <v>0.1801029656870475</v>
       </c>
       <c r="T80">
-        <v>2.960699432529915</v>
+        <v>3.101685119793244</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07371941594208718</v>
+        <v>0.07278625877826329</v>
       </c>
       <c r="W80">
-        <v>0.1859971412788289</v>
+        <v>0.1861845192373247</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.245731386473624</v>
+        <v>0.242620862594211</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8280,22 +8280,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1849073929917665</v>
+        <v>0.1864573929917666</v>
       </c>
       <c r="C81">
-        <v>-4042.323422281358</v>
+        <v>-4127.773771747941</v>
       </c>
       <c r="D81">
-        <v>1284.460577718643</v>
+        <v>1270.306228252059</v>
       </c>
       <c r="E81">
-        <v>4192.184</v>
+        <v>4263.48</v>
       </c>
       <c r="F81">
-        <v>5632.384</v>
+        <v>5703.68</v>
       </c>
       <c r="G81">
         <v>305.6</v>
@@ -8316,37 +8316,37 @@
         <v>274.4</v>
       </c>
       <c r="M81">
-        <v>1130.9827072</v>
+        <v>1145.298944</v>
       </c>
       <c r="N81">
-        <v>-856.5827072000001</v>
+        <v>-870.8989440000001</v>
       </c>
       <c r="O81">
-        <v>-256.97481216</v>
+        <v>-261.2696832</v>
       </c>
       <c r="P81">
-        <v>-599.6078950400001</v>
+        <v>-609.6292608000001</v>
       </c>
       <c r="Q81">
-        <v>-544.8078950400002</v>
+        <v>-554.8292608000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1801029656870475</v>
+        <v>0.1868181139713999</v>
       </c>
       <c r="T81">
-        <v>3.101685119793244</v>
+        <v>3.256769375782907</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.07278625877826329</v>
+        <v>0.071876430543535</v>
       </c>
       <c r="W81">
-        <v>0.1861845192373247</v>
+        <v>0.1863672127468582</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.242620862594211</v>
+        <v>0.2395881018117834</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8362,22 +8362,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1864573929917666</v>
+        <v>0.1880073929917665</v>
       </c>
       <c r="C82">
-        <v>-4127.773771747941</v>
+        <v>-4212.915568456306</v>
       </c>
       <c r="D82">
-        <v>1270.306228252059</v>
+        <v>1256.460431543694</v>
       </c>
       <c r="E82">
-        <v>4263.48</v>
+        <v>4334.776</v>
       </c>
       <c r="F82">
-        <v>5703.68</v>
+        <v>5774.976</v>
       </c>
       <c r="G82">
         <v>305.6</v>
@@ -8398,37 +8398,37 @@
         <v>274.4</v>
       </c>
       <c r="M82">
-        <v>1145.298944</v>
+        <v>1159.6151808</v>
       </c>
       <c r="N82">
-        <v>-870.8989440000001</v>
+        <v>-885.2151808</v>
       </c>
       <c r="O82">
-        <v>-261.2696832</v>
+        <v>-265.56455424</v>
       </c>
       <c r="P82">
-        <v>-609.6292608000001</v>
+        <v>-619.65062656</v>
       </c>
       <c r="Q82">
-        <v>-554.8292608000002</v>
+        <v>-564.8506265599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1868181139713999</v>
+        <v>0.1942401199698946</v>
       </c>
       <c r="T82">
-        <v>3.256769375782907</v>
+        <v>3.428178290297796</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.071876430543535</v>
+        <v>0.07098906720349137</v>
       </c>
       <c r="W82">
-        <v>0.1863672127468582</v>
+        <v>0.1865453953055389</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2395881018117834</v>
+        <v>0.2366302240116379</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8444,22 +8444,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1880073929917665</v>
+        <v>0.1895573929917665</v>
       </c>
       <c r="C83">
-        <v>-4212.915568456306</v>
+        <v>-4297.758792904124</v>
       </c>
       <c r="D83">
-        <v>1256.460431543694</v>
+        <v>1242.913207095876</v>
       </c>
       <c r="E83">
-        <v>4334.776</v>
+        <v>4406.072</v>
       </c>
       <c r="F83">
-        <v>5774.976</v>
+        <v>5846.272</v>
       </c>
       <c r="G83">
         <v>305.6</v>
@@ -8480,37 +8480,37 @@
         <v>274.4</v>
       </c>
       <c r="M83">
-        <v>1159.6151808</v>
+        <v>1173.9314176</v>
       </c>
       <c r="N83">
-        <v>-885.2151808</v>
+        <v>-899.5314176000001</v>
       </c>
       <c r="O83">
-        <v>-265.56455424</v>
+        <v>-269.85942528</v>
       </c>
       <c r="P83">
-        <v>-619.65062656</v>
+        <v>-629.6719923200001</v>
       </c>
       <c r="Q83">
-        <v>-564.8506265599999</v>
+        <v>-574.8719923200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1942401199698946</v>
+        <v>0.2024867933015554</v>
       </c>
       <c r="T83">
-        <v>3.428178290297796</v>
+        <v>3.618632639758785</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.07098906720349137</v>
+        <v>0.07012334687174147</v>
       </c>
       <c r="W83">
-        <v>0.1865453953055389</v>
+        <v>0.1867192319481543</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2366302240116379</v>
+        <v>0.2337444895724716</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8526,22 +8526,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1895573929917665</v>
+        <v>0.1911073929917665</v>
       </c>
       <c r="C84">
-        <v>-4297.758792904124</v>
+        <v>-4382.312999739532</v>
       </c>
       <c r="D84">
-        <v>1242.913207095876</v>
+        <v>1229.655000260469</v>
       </c>
       <c r="E84">
-        <v>4406.072</v>
+        <v>4477.368</v>
       </c>
       <c r="F84">
-        <v>5846.272</v>
+        <v>5917.568</v>
       </c>
       <c r="G84">
         <v>305.6</v>
@@ -8562,37 +8562,37 @@
         <v>274.4</v>
       </c>
       <c r="M84">
-        <v>1173.9314176</v>
+        <v>1188.2476544</v>
       </c>
       <c r="N84">
-        <v>-899.5314176000001</v>
+        <v>-913.8476544000001</v>
       </c>
       <c r="O84">
-        <v>-269.85942528</v>
+        <v>-274.15429632</v>
       </c>
       <c r="P84">
-        <v>-629.6719923200001</v>
+        <v>-639.6933580800001</v>
       </c>
       <c r="Q84">
-        <v>-574.8719923200001</v>
+        <v>-584.8933580800001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2024867933015554</v>
+        <v>0.2117036634957646</v>
       </c>
       <c r="T84">
-        <v>3.618632639758785</v>
+        <v>3.831493383274008</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07012334687174147</v>
+        <v>0.06927848727087711</v>
       </c>
       <c r="W84">
-        <v>0.1867192319481543</v>
+        <v>0.1868888797560079</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2337444895724716</v>
+        <v>0.2309282909029237</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1911073929917665</v>
+        <v>0.1926573929917665</v>
       </c>
       <c r="C85">
-        <v>-4382.312999739532</v>
+        <v>-4466.587340234182</v>
       </c>
       <c r="D85">
-        <v>1229.655000260469</v>
+        <v>1216.676659765818</v>
       </c>
       <c r="E85">
-        <v>4477.368</v>
+        <v>4548.664000000001</v>
       </c>
       <c r="F85">
-        <v>5917.568</v>
+        <v>5988.864</v>
       </c>
       <c r="G85">
         <v>305.6</v>
@@ -8644,37 +8644,37 @@
         <v>274.4</v>
       </c>
       <c r="M85">
-        <v>1188.2476544</v>
+        <v>1202.5638912</v>
       </c>
       <c r="N85">
-        <v>-913.8476544000001</v>
+        <v>-928.1638912000002</v>
       </c>
       <c r="O85">
-        <v>-274.15429632</v>
+        <v>-278.44916736</v>
       </c>
       <c r="P85">
-        <v>-639.6933580800001</v>
+        <v>-649.7147238400001</v>
       </c>
       <c r="Q85">
-        <v>-584.8933580800001</v>
+        <v>-594.9147238400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2117036634957646</v>
+        <v>0.2220726424642499</v>
       </c>
       <c r="T85">
-        <v>3.831493383274008</v>
+        <v>4.070961719728635</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.06927848727087711</v>
+        <v>0.06845374337479523</v>
       </c>
       <c r="W85">
-        <v>0.1868888797560079</v>
+        <v>0.1870544883303411</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2309282909029237</v>
+        <v>0.2281791445826508</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8690,22 +8690,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1926573929917665</v>
+        <v>0.1942073929917665</v>
       </c>
       <c r="C86">
-        <v>-4466.58734023418</v>
+        <v>-4550.590583348016</v>
       </c>
       <c r="D86">
-        <v>1216.676659765819</v>
+        <v>1203.969416651982</v>
       </c>
       <c r="E86">
-        <v>4548.664</v>
+        <v>4619.959999999999</v>
       </c>
       <c r="F86">
-        <v>5988.864</v>
+        <v>6060.159999999999</v>
       </c>
       <c r="G86">
         <v>305.6</v>
@@ -8726,37 +8726,37 @@
         <v>274.4</v>
       </c>
       <c r="M86">
-        <v>1202.5638912</v>
+        <v>1216.880128</v>
       </c>
       <c r="N86">
-        <v>-928.1638912</v>
+        <v>-942.4801279999998</v>
       </c>
       <c r="O86">
-        <v>-278.44916736</v>
+        <v>-282.7440383999999</v>
       </c>
       <c r="P86">
-        <v>-649.71472384</v>
+        <v>-659.7360895999999</v>
       </c>
       <c r="Q86">
-        <v>-594.9147238400001</v>
+        <v>-604.9360895999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2220726424642498</v>
+        <v>0.2338241519618665</v>
       </c>
       <c r="T86">
-        <v>4.070961719728632</v>
+        <v>4.342359167710541</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.06845374337479525</v>
+        <v>0.06764840521744472</v>
       </c>
       <c r="W86">
-        <v>0.1870544883303411</v>
+        <v>0.1872162002323371</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2281791445826509</v>
+        <v>0.2254946840581491</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8772,22 +8772,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1942073929917665</v>
+        <v>0.1957573929917665</v>
       </c>
       <c r="C87">
-        <v>-4550.590583348016</v>
+        <v>-4634.331135487657</v>
       </c>
       <c r="D87">
-        <v>1203.969416651982</v>
+        <v>1191.524864512342</v>
       </c>
       <c r="E87">
-        <v>4619.959999999999</v>
+        <v>4691.255999999999</v>
       </c>
       <c r="F87">
-        <v>6060.159999999999</v>
+        <v>6131.455999999999</v>
       </c>
       <c r="G87">
         <v>305.6</v>
@@ -8808,37 +8808,37 @@
         <v>274.4</v>
       </c>
       <c r="M87">
-        <v>1216.880128</v>
+        <v>1231.1963648</v>
       </c>
       <c r="N87">
-        <v>-942.4801279999998</v>
+        <v>-956.7963647999999</v>
       </c>
       <c r="O87">
-        <v>-282.7440383999999</v>
+        <v>-287.0389094399999</v>
       </c>
       <c r="P87">
-        <v>-659.7360895999999</v>
+        <v>-669.75745536</v>
       </c>
       <c r="Q87">
-        <v>-604.9360895999998</v>
+        <v>-614.95745536</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2338241519618665</v>
+        <v>0.2472544485305712</v>
       </c>
       <c r="T87">
-        <v>4.342359167710541</v>
+        <v>4.652527679689865</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.06764840521744472</v>
+        <v>0.06686179585445118</v>
       </c>
       <c r="W87">
-        <v>0.1872162002323371</v>
+        <v>0.1873741513924262</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2254946840581491</v>
+        <v>0.2228726528481706</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8854,22 +8854,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1957573929917665</v>
+        <v>0.1973073929917665</v>
       </c>
       <c r="C88">
-        <v>-4634.331135487657</v>
+        <v>-4717.817059051945</v>
       </c>
       <c r="D88">
-        <v>1191.524864512342</v>
+        <v>1179.334940948055</v>
       </c>
       <c r="E88">
-        <v>4691.255999999999</v>
+        <v>4762.552</v>
       </c>
       <c r="F88">
-        <v>6131.455999999999</v>
+        <v>6202.751999999999</v>
       </c>
       <c r="G88">
         <v>305.6</v>
@@ -8890,37 +8890,37 @@
         <v>274.4</v>
       </c>
       <c r="M88">
-        <v>1231.1963648</v>
+        <v>1245.5126016</v>
       </c>
       <c r="N88">
-        <v>-956.7963647999999</v>
+        <v>-971.1126015999999</v>
       </c>
       <c r="O88">
-        <v>-287.0389094399999</v>
+        <v>-291.33378048</v>
       </c>
       <c r="P88">
-        <v>-669.75745536</v>
+        <v>-679.77882112</v>
       </c>
       <c r="Q88">
-        <v>-614.95745536</v>
+        <v>-624.97882112</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2472544485305712</v>
+        <v>0.2627509445713844</v>
       </c>
       <c r="T88">
-        <v>4.652527679689865</v>
+        <v>5.010414424281393</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.06686179585445118</v>
+        <v>0.06609326946531954</v>
       </c>
       <c r="W88">
-        <v>0.1873741513924262</v>
+        <v>0.1875284714913638</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2228726528481706</v>
+        <v>0.2203108982177319</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8936,22 +8936,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1973073929917665</v>
+        <v>0.1988573929917665</v>
       </c>
       <c r="C89">
-        <v>-4717.817059051945</v>
+        <v>-4801.056089850646</v>
       </c>
       <c r="D89">
-        <v>1179.334940948055</v>
+        <v>1167.391910149354</v>
       </c>
       <c r="E89">
-        <v>4762.552</v>
+        <v>4833.848</v>
       </c>
       <c r="F89">
-        <v>6202.751999999999</v>
+        <v>6274.048</v>
       </c>
       <c r="G89">
         <v>305.6</v>
@@ -8972,37 +8972,37 @@
         <v>274.4</v>
       </c>
       <c r="M89">
-        <v>1245.5126016</v>
+        <v>1259.8288384</v>
       </c>
       <c r="N89">
-        <v>-971.1126015999999</v>
+        <v>-985.4288384</v>
       </c>
       <c r="O89">
-        <v>-291.33378048</v>
+        <v>-295.62865152</v>
       </c>
       <c r="P89">
-        <v>-679.77882112</v>
+        <v>-689.80018688</v>
       </c>
       <c r="Q89">
-        <v>-624.97882112</v>
+        <v>-635.00018688</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2627509445713844</v>
+        <v>0.2808301899523331</v>
       </c>
       <c r="T89">
-        <v>5.010414424281393</v>
+        <v>5.427948959638177</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.06609326946531954</v>
+        <v>0.06534220958503183</v>
       </c>
       <c r="W89">
-        <v>0.1875284714913638</v>
+        <v>0.1876792843153256</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2203108982177319</v>
+        <v>0.2178073652834395</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9018,22 +9018,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1988573929917665</v>
+        <v>0.2004073929917665</v>
       </c>
       <c r="C90">
-        <v>-4801.056089850646</v>
+        <v>-4884.055653475368</v>
       </c>
       <c r="D90">
-        <v>1167.391910149354</v>
+        <v>1155.688346524632</v>
       </c>
       <c r="E90">
-        <v>4833.848</v>
+        <v>4905.144</v>
       </c>
       <c r="F90">
-        <v>6274.048</v>
+        <v>6345.344</v>
       </c>
       <c r="G90">
         <v>305.6</v>
@@ -9054,37 +9054,37 @@
         <v>274.4</v>
       </c>
       <c r="M90">
-        <v>1259.8288384</v>
+        <v>1274.1450752</v>
       </c>
       <c r="N90">
-        <v>-985.4288384</v>
+        <v>-999.7450752000001</v>
       </c>
       <c r="O90">
-        <v>-295.62865152</v>
+        <v>-299.92352256</v>
       </c>
       <c r="P90">
-        <v>-689.80018688</v>
+        <v>-699.82155264</v>
       </c>
       <c r="Q90">
-        <v>-635.00018688</v>
+        <v>-645.02155264</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2808301899523331</v>
+        <v>0.3021965708570906</v>
       </c>
       <c r="T90">
-        <v>5.427948959638177</v>
+        <v>5.921398865059828</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.06534220958503183</v>
+        <v>0.06460802745486292</v>
       </c>
       <c r="W90">
-        <v>0.1876792843153256</v>
+        <v>0.1878267080870635</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2178073652834395</v>
+        <v>0.2153600915162097</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9100,22 +9100,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2004073929917665</v>
+        <v>0.2019573929917665</v>
       </c>
       <c r="C91">
-        <v>-4884.055653475368</v>
+        <v>-4966.822880695507</v>
       </c>
       <c r="D91">
-        <v>1155.688346524632</v>
+        <v>1144.217119304493</v>
       </c>
       <c r="E91">
-        <v>4905.144</v>
+        <v>4976.44</v>
       </c>
       <c r="F91">
-        <v>6345.344</v>
+        <v>6416.639999999999</v>
       </c>
       <c r="G91">
         <v>305.6</v>
@@ -9136,37 +9136,37 @@
         <v>274.4</v>
       </c>
       <c r="M91">
-        <v>1274.1450752</v>
+        <v>1288.461312</v>
       </c>
       <c r="N91">
-        <v>-999.7450752000001</v>
+        <v>-1014.061312</v>
       </c>
       <c r="O91">
-        <v>-299.92352256</v>
+        <v>-304.2183936</v>
       </c>
       <c r="P91">
-        <v>-699.82155264</v>
+        <v>-709.8429183999999</v>
       </c>
       <c r="Q91">
-        <v>-645.02155264</v>
+        <v>-655.0429184</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3021965708570906</v>
+        <v>0.3278362279427998</v>
       </c>
       <c r="T91">
-        <v>5.921398865059828</v>
+        <v>6.513538751565813</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.06460802745486292</v>
+        <v>0.06389016048314224</v>
       </c>
       <c r="W91">
-        <v>0.1878267080870635</v>
+        <v>0.187970855774985</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2153600915162097</v>
+        <v>0.2129672016104741</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9182,22 +9182,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2019573929917665</v>
+        <v>0.2035073929917665</v>
       </c>
       <c r="C92">
-        <v>-4966.822880695507</v>
+        <v>-5049.364621946297</v>
       </c>
       <c r="D92">
-        <v>1144.217119304493</v>
+        <v>1132.971378053703</v>
       </c>
       <c r="E92">
-        <v>4976.44</v>
+        <v>5047.736</v>
       </c>
       <c r="F92">
-        <v>6416.639999999999</v>
+        <v>6487.936</v>
       </c>
       <c r="G92">
         <v>305.6</v>
@@ -9218,37 +9218,37 @@
         <v>274.4</v>
       </c>
       <c r="M92">
-        <v>1288.461312</v>
+        <v>1302.7775488</v>
       </c>
       <c r="N92">
-        <v>-1014.061312</v>
+        <v>-1028.3775488</v>
       </c>
       <c r="O92">
-        <v>-304.2183936</v>
+        <v>-308.51326464</v>
       </c>
       <c r="P92">
-        <v>-709.8429183999999</v>
+        <v>-719.8642841600001</v>
       </c>
       <c r="Q92">
-        <v>-655.0429184</v>
+        <v>-665.0642841600002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3278362279427998</v>
+        <v>0.3591735866031109</v>
       </c>
       <c r="T92">
-        <v>6.513538751565813</v>
+        <v>7.237265279517571</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.06389016048314224</v>
+        <v>0.0631880708075033</v>
       </c>
       <c r="W92">
-        <v>0.187970855774985</v>
+        <v>0.1881118353818533</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2129672016104741</v>
+        <v>0.2106269026916776</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9264,22 +9264,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2035073929917665</v>
+        <v>0.2050573929917665</v>
       </c>
       <c r="C93">
-        <v>-5049.364621946297</v>
+        <v>-5131.687460970806</v>
       </c>
       <c r="D93">
-        <v>1132.971378053703</v>
+        <v>1121.944539029194</v>
       </c>
       <c r="E93">
-        <v>5047.736</v>
+        <v>5119.032</v>
       </c>
       <c r="F93">
-        <v>6487.936</v>
+        <v>6559.232</v>
       </c>
       <c r="G93">
         <v>305.6</v>
@@ -9300,37 +9300,37 @@
         <v>274.4</v>
       </c>
       <c r="M93">
-        <v>1302.7775488</v>
+        <v>1317.0937856</v>
       </c>
       <c r="N93">
-        <v>-1028.3775488</v>
+        <v>-1042.6937856</v>
       </c>
       <c r="O93">
-        <v>-308.51326464</v>
+        <v>-312.80813568</v>
       </c>
       <c r="P93">
-        <v>-719.8642841600001</v>
+        <v>-729.88564992</v>
       </c>
       <c r="Q93">
-        <v>-665.0642841600002</v>
+        <v>-675.0856499199999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3591735866031109</v>
+        <v>0.3983452849284999</v>
       </c>
       <c r="T93">
-        <v>7.237265279517571</v>
+        <v>8.141923439457269</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0631880708075033</v>
+        <v>0.06250124395090001</v>
       </c>
       <c r="W93">
-        <v>0.1881118353818533</v>
+        <v>0.1882497502146593</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2106269026916776</v>
+        <v>0.2083374798363334</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9346,22 +9346,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2050573929917665</v>
+        <v>0.2066073929917665</v>
       </c>
       <c r="C94">
-        <v>-5131.687460970806</v>
+        <v>-5213.797727672987</v>
       </c>
       <c r="D94">
-        <v>1121.944539029194</v>
+        <v>1111.130272327014</v>
       </c>
       <c r="E94">
-        <v>5119.032</v>
+        <v>5190.328</v>
       </c>
       <c r="F94">
-        <v>6559.232</v>
+        <v>6630.528</v>
       </c>
       <c r="G94">
         <v>305.6</v>
@@ -9382,37 +9382,37 @@
         <v>274.4</v>
       </c>
       <c r="M94">
-        <v>1317.0937856</v>
+        <v>1331.4100224</v>
       </c>
       <c r="N94">
-        <v>-1042.6937856</v>
+        <v>-1057.0100224</v>
       </c>
       <c r="O94">
-        <v>-312.80813568</v>
+        <v>-317.1030067200001</v>
       </c>
       <c r="P94">
-        <v>-729.88564992</v>
+        <v>-739.9070156800002</v>
       </c>
       <c r="Q94">
-        <v>-675.0856499199999</v>
+        <v>-685.1070156800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3983452849284999</v>
+        <v>0.4487088970611427</v>
       </c>
       <c r="T94">
-        <v>8.141923439457269</v>
+        <v>9.305055359379736</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.06250124395090001</v>
+        <v>0.06182918756433119</v>
       </c>
       <c r="W94">
-        <v>0.1882497502146593</v>
+        <v>0.1883846991370823</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2083374798363334</v>
+        <v>0.2060972918811038</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9428,22 +9428,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2066073929917665</v>
+        <v>0.2081573929917666</v>
       </c>
       <c r="C95">
-        <v>-5213.797727672987</v>
+        <v>-5295.701510234476</v>
       </c>
       <c r="D95">
-        <v>1111.130272327014</v>
+        <v>1100.522489765524</v>
       </c>
       <c r="E95">
-        <v>5190.328</v>
+        <v>5261.624</v>
       </c>
       <c r="F95">
-        <v>6630.528</v>
+        <v>6701.824</v>
       </c>
       <c r="G95">
         <v>305.6</v>
@@ -9464,37 +9464,37 @@
         <v>274.4</v>
       </c>
       <c r="M95">
-        <v>1331.4100224</v>
+        <v>1345.7262592</v>
       </c>
       <c r="N95">
-        <v>-1057.0100224</v>
+        <v>-1071.3262592</v>
       </c>
       <c r="O95">
-        <v>-317.1030067200001</v>
+        <v>-321.39787776</v>
       </c>
       <c r="P95">
-        <v>-739.9070156800002</v>
+        <v>-749.9283814400001</v>
       </c>
       <c r="Q95">
-        <v>-685.1070156800001</v>
+        <v>-695.1283814400001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4487088970611427</v>
+        <v>0.5158603799046667</v>
       </c>
       <c r="T95">
-        <v>9.305055359379736</v>
+        <v>10.85589791927636</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06182918756433119</v>
+        <v>0.06117143024981703</v>
       </c>
       <c r="W95">
-        <v>0.1883846991370823</v>
+        <v>0.1885167768058368</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2060972918811038</v>
+        <v>0.20390476749939</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9510,22 +9510,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2081573929917666</v>
+        <v>0.2097073929917665</v>
       </c>
       <c r="C96">
-        <v>-5295.701510234476</v>
+        <v>-5377.404666543905</v>
       </c>
       <c r="D96">
-        <v>1100.522489765524</v>
+        <v>1090.115333456094</v>
       </c>
       <c r="E96">
-        <v>5261.624</v>
+        <v>5332.92</v>
       </c>
       <c r="F96">
-        <v>6701.824</v>
+        <v>6773.12</v>
       </c>
       <c r="G96">
         <v>305.6</v>
@@ -9546,37 +9546,37 @@
         <v>274.4</v>
       </c>
       <c r="M96">
-        <v>1345.7262592</v>
+        <v>1360.042496</v>
       </c>
       <c r="N96">
-        <v>-1071.3262592</v>
+        <v>-1085.642496</v>
       </c>
       <c r="O96">
-        <v>-321.39787776</v>
+        <v>-325.6927487999999</v>
       </c>
       <c r="P96">
-        <v>-749.9283814400001</v>
+        <v>-759.9497472</v>
       </c>
       <c r="Q96">
-        <v>-695.1283814400001</v>
+        <v>-705.1497472000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5158603799046667</v>
+        <v>0.6098724558856002</v>
       </c>
       <c r="T96">
-        <v>10.85589791927636</v>
+        <v>13.02707750313164</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06117143024981703</v>
+        <v>0.06052752045771369</v>
       </c>
       <c r="W96">
-        <v>0.1885167768058368</v>
+        <v>0.1886460738920911</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.20390476749939</v>
+        <v>0.2017584015257123</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9592,22 +9592,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2097073929917665</v>
+        <v>0.2451127952883586</v>
       </c>
       <c r="C97">
-        <v>-5377.404666543905</v>
+        <v>-5642.345895766934</v>
       </c>
       <c r="D97">
-        <v>1090.115333456094</v>
+        <v>896.4701042330666</v>
       </c>
       <c r="E97">
-        <v>5332.92</v>
+        <v>5404.216</v>
       </c>
       <c r="F97">
-        <v>6773.12</v>
+        <v>6844.416</v>
       </c>
       <c r="G97">
         <v>305.6</v>
@@ -9628,45 +9628,45 @@
         <v>274.4</v>
       </c>
       <c r="M97">
-        <v>1360.042496</v>
+        <v>1613.9132928</v>
       </c>
       <c r="N97">
-        <v>-1085.642496</v>
+        <v>-1339.5132928</v>
       </c>
       <c r="O97">
-        <v>-325.6927487999999</v>
+        <v>-401.8539878400001</v>
       </c>
       <c r="P97">
-        <v>-759.9497472</v>
+        <v>-937.6593049600002</v>
       </c>
       <c r="Q97">
-        <v>-705.1497472000001</v>
+        <v>-882.8593049600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6098724558856002</v>
+        <v>0.7572756272718016</v>
       </c>
       <c r="T97">
-        <v>13.02707750313164</v>
+        <v>16.4313077891871</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06052752045771369</v>
+        <v>0.05100645763762309</v>
       </c>
       <c r="W97">
-        <v>0.1886460738920911</v>
+        <v>0.2237726772890485</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.2017584015257123</v>
+        <v>0.1700215254587436</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9674,22 +9674,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2451127952883585</v>
+        <v>0.2470127952883586</v>
       </c>
       <c r="C98">
-        <v>-5642.345895766933</v>
+        <v>-5722.107029386303</v>
       </c>
       <c r="D98">
-        <v>896.4701042330666</v>
+        <v>888.004970613697</v>
       </c>
       <c r="E98">
-        <v>5404.215999999999</v>
+        <v>5475.512</v>
       </c>
       <c r="F98">
-        <v>6844.415999999999</v>
+        <v>6915.712</v>
       </c>
       <c r="G98">
         <v>305.6</v>
@@ -9710,37 +9710,37 @@
         <v>274.4</v>
       </c>
       <c r="M98">
-        <v>1613.9132928</v>
+        <v>1630.7248896</v>
       </c>
       <c r="N98">
-        <v>-1339.5132928</v>
+        <v>-1356.3248896</v>
       </c>
       <c r="O98">
-        <v>-401.8539878399999</v>
+        <v>-406.89746688</v>
       </c>
       <c r="P98">
-        <v>-937.6593049599999</v>
+        <v>-949.4274227200001</v>
       </c>
       <c r="Q98">
-        <v>-882.8593049599999</v>
+        <v>-894.6274227200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7572756272717996</v>
+        <v>0.9944341696957331</v>
       </c>
       <c r="T98">
-        <v>16.43130778918706</v>
+        <v>21.90841038558274</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0510064576376231</v>
+        <v>0.05048061786816306</v>
       </c>
       <c r="W98">
-        <v>0.2237726772890485</v>
+        <v>0.2238966703066872</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1700215254587437</v>
+        <v>0.1682687262272101</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9756,22 +9756,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2470127952883586</v>
+        <v>0.2489127952883586</v>
       </c>
       <c r="C99">
-        <v>-5722.107029386303</v>
+        <v>-5801.7097903748</v>
       </c>
       <c r="D99">
-        <v>888.004970613697</v>
+        <v>879.6982096251995</v>
       </c>
       <c r="E99">
-        <v>5475.512</v>
+        <v>5546.807999999999</v>
       </c>
       <c r="F99">
-        <v>6915.712</v>
+        <v>6987.007999999999</v>
       </c>
       <c r="G99">
         <v>305.6</v>
@@ -9792,37 +9792,37 @@
         <v>274.4</v>
       </c>
       <c r="M99">
-        <v>1630.7248896</v>
+        <v>1647.5364864</v>
       </c>
       <c r="N99">
-        <v>-1356.3248896</v>
+        <v>-1373.1364864</v>
       </c>
       <c r="O99">
-        <v>-406.89746688</v>
+        <v>-411.9409459199999</v>
       </c>
       <c r="P99">
-        <v>-949.4274227200001</v>
+        <v>-961.1955404799999</v>
       </c>
       <c r="Q99">
-        <v>-894.6274227200001</v>
+        <v>-906.3955404799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9944341696957331</v>
+        <v>1.468751254543599</v>
       </c>
       <c r="T99">
-        <v>21.90841038558274</v>
+        <v>32.86261557837411</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05048061786816306</v>
+        <v>0.04996550952256956</v>
       </c>
       <c r="W99">
-        <v>0.2238966703066872</v>
+        <v>0.2240181328545781</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1682687262272101</v>
+        <v>0.1665516984085653</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9838,22 +9838,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2489127952883586</v>
+        <v>0.2508127952883585</v>
       </c>
       <c r="C100">
-        <v>-5801.7097903748</v>
+        <v>-5881.158581989279</v>
       </c>
       <c r="D100">
-        <v>879.6982096251995</v>
+        <v>871.5454180107198</v>
       </c>
       <c r="E100">
-        <v>5546.807999999999</v>
+        <v>5618.103999999999</v>
       </c>
       <c r="F100">
-        <v>6987.007999999999</v>
+        <v>7058.303999999999</v>
       </c>
       <c r="G100">
         <v>305.6</v>
@@ -9874,37 +9874,37 @@
         <v>274.4</v>
       </c>
       <c r="M100">
-        <v>1647.5364864</v>
+        <v>1664.3480832</v>
       </c>
       <c r="N100">
-        <v>-1373.1364864</v>
+        <v>-1389.9480832</v>
       </c>
       <c r="O100">
-        <v>-411.9409459199999</v>
+        <v>-416.98442496</v>
       </c>
       <c r="P100">
-        <v>-961.1955404799999</v>
+        <v>-972.96365824</v>
       </c>
       <c r="Q100">
-        <v>-906.3955404799999</v>
+        <v>-918.1636582399999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.468751254543599</v>
+        <v>2.891702509087199</v>
       </c>
       <c r="T100">
-        <v>32.86261557837411</v>
+        <v>65.72523115674822</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04996550952256956</v>
+        <v>0.04946080740617997</v>
       </c>
       <c r="W100">
-        <v>0.2240181328545781</v>
+        <v>0.2241371416136228</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9912,91 +9912,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1665516984085653</v>
+        <v>0.1648693580205999</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2508127952883585</v>
-      </c>
-      <c r="C101">
-        <v>-5881.158581989279</v>
-      </c>
-      <c r="D101">
-        <v>871.5454180107198</v>
-      </c>
-      <c r="E101">
-        <v>5618.103999999999</v>
-      </c>
-      <c r="F101">
-        <v>7058.303999999999</v>
-      </c>
-      <c r="G101">
-        <v>305.6</v>
-      </c>
-      <c r="H101">
-        <v>5689.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>329.2</v>
-      </c>
-      <c r="K101">
-        <v>54.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>274.4</v>
-      </c>
-      <c r="M101">
-        <v>1664.3480832</v>
-      </c>
-      <c r="N101">
-        <v>-1389.9480832</v>
-      </c>
-      <c r="O101">
-        <v>-416.98442496</v>
-      </c>
-      <c r="P101">
-        <v>-972.96365824</v>
-      </c>
-      <c r="Q101">
-        <v>-918.1636582399999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.891702509087199</v>
-      </c>
-      <c r="T101">
-        <v>65.72523115674822</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04946080740617997</v>
-      </c>
-      <c r="W101">
-        <v>0.2241371416136228</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1648693580205999</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
